--- a/S-158-111/1.1.0/WD-158_111_1_1_0_20260930.xlsx
+++ b/S-158-111/1.1.0/WD-158_111_1_1_0_20260930.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\TWCWG\S-158-111\1.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4203EFBB-41D4-49E6-BE7C-627A7F2BCB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D942AE84-7DF8-43DA-8525-0D9A7DE9EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" activeTab="1" xr2:uid="{D500D42E-56ED-44C2-B321-3F3845968AA3}"/>
   </bookViews>
@@ -2055,9 +2055,6 @@
     <t>IF the bounding box of one &lt;FINST&gt; overlaps with another &lt;FINST&gt;</t>
   </si>
   <si>
-    <t>To be modified when scale ranges are introduced</t>
-  </si>
-  <si>
     <r>
       <t>N/</t>
     </r>
@@ -2098,30 +2095,6 @@
   </si>
   <si>
     <t>111_5035</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dataset file size exceeds 10MB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.
-Feature exceeds size limit</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2323,6 +2296,43 @@
   </si>
   <si>
     <t>S-111 2.0 restricts interpolation type to 'discrete'.</t>
+  </si>
+  <si>
+    <t>Compares features in the same dataset only</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dataset file size exceeds 10MB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Feature exceeds size limit</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3366,7 +3376,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3613,7 +3623,7 @@
         <v>208</v>
       </c>
       <c r="M1" s="100" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="N1" s="78" t="s">
         <v>231</v>
@@ -3656,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="O2" s="59" t="s">
         <v>233</v>
@@ -3693,10 +3703,10 @@
       <c r="J3" s="36"/>
       <c r="K3" s="36"/>
       <c r="M3" s="102" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="O3" s="59" t="s">
         <v>43</v>
@@ -3768,10 +3778,10 @@
       <c r="J5" s="36"/>
       <c r="K5" s="36"/>
       <c r="M5" s="102" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="N5" s="42" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="O5" s="59" t="s">
         <v>43</v>
@@ -3811,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="42" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="O6" s="59" t="s">
         <v>235</v>
@@ -3851,7 +3861,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="42" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="O7" s="59" t="s">
         <v>235</v>
@@ -3891,7 +3901,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="42" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="O8" s="59" t="s">
         <v>236</v>
@@ -3966,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="42" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="O10" s="59" t="s">
         <v>237</v>
@@ -4006,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="42" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>237</v>
@@ -4043,7 +4053,7 @@
       <c r="J12" s="36"/>
       <c r="K12" s="36"/>
       <c r="N12" s="42" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>390</v>
@@ -4080,7 +4090,7 @@
       <c r="J13" s="36"/>
       <c r="K13" s="36"/>
       <c r="N13" s="42" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="O13" s="59" t="s">
         <v>238</v>
@@ -4117,7 +4127,7 @@
       <c r="J14" s="36"/>
       <c r="K14" s="36"/>
       <c r="N14" s="42" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="O14" s="59" t="s">
         <v>390</v>
@@ -4269,7 +4279,7 @@
       <c r="L18" s="83"/>
       <c r="M18" s="102"/>
       <c r="N18" s="85" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O18" s="86" t="s">
         <v>43</v>
@@ -4307,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="O19" s="59" t="s">
         <v>239</v>
@@ -4342,7 +4352,7 @@
         <v>277</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="O20" s="59" t="s">
         <v>239</v>
@@ -4378,7 +4388,7 @@
       </c>
       <c r="L21" s="46"/>
       <c r="N21" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="O21" s="59" t="s">
         <v>239</v>
@@ -4722,7 +4732,7 @@
       </c>
       <c r="L31" s="46"/>
       <c r="N31" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="O31" s="59" t="s">
         <v>240</v>
@@ -4970,10 +4980,10 @@
       </c>
       <c r="L38" s="46"/>
       <c r="M38" s="102" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="O38" s="59" t="s">
         <v>239</v>
@@ -5152,7 +5162,7 @@
       </c>
       <c r="L43" s="46"/>
       <c r="N43" s="85" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
@@ -5226,7 +5236,7 @@
         <v>402</v>
       </c>
       <c r="O45" s="59" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
@@ -5260,10 +5270,10 @@
       <c r="J46" s="83"/>
       <c r="K46" s="83"/>
       <c r="L46" s="83"/>
-      <c r="M46" s="102"/>
-      <c r="N46" s="85" t="s">
-        <v>604</v>
-      </c>
+      <c r="M46" s="102" t="s">
+        <v>647</v>
+      </c>
+      <c r="N46" s="85"/>
       <c r="O46" s="86"/>
     </row>
     <row r="47" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
@@ -5471,7 +5481,7 @@
       <c r="J52" s="36"/>
       <c r="K52" s="36"/>
       <c r="N52" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="O52" s="59" t="s">
         <v>242</v>
@@ -5616,7 +5626,7 @@
         <v>255</v>
       </c>
       <c r="O56" s="59" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="51" x14ac:dyDescent="0.2">
@@ -5650,7 +5660,7 @@
       <c r="J57" s="36"/>
       <c r="K57" s="36"/>
       <c r="N57" s="95" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="O57" s="59" t="s">
         <v>242</v>
@@ -5690,7 +5700,7 @@
         <v>256</v>
       </c>
       <c r="O58" s="59" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
@@ -5727,7 +5737,7 @@
         <v>257</v>
       </c>
       <c r="O59" s="59" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
@@ -6209,7 +6219,7 @@
       </c>
       <c r="L73" s="88"/>
       <c r="N73" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -6485,7 +6495,7 @@
       </c>
       <c r="L81" s="46"/>
       <c r="N81" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="O81" s="59" t="s">
         <v>240</v>
@@ -6493,16 +6503,16 @@
     </row>
     <row r="82" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="83" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B82" s="84" t="s">
         <v>449</v>
       </c>
       <c r="C82" s="80" t="s">
+        <v>606</v>
+      </c>
+      <c r="D82" s="81" t="s">
         <v>607</v>
-      </c>
-      <c r="D82" s="81" t="s">
-        <v>608</v>
       </c>
       <c r="E82" s="80" t="s">
         <v>146</v>
@@ -6511,7 +6521,7 @@
         <v>232</v>
       </c>
       <c r="G82" s="82" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H82" s="80"/>
       <c r="I82" s="83" t="s">
@@ -6522,7 +6532,7 @@
       <c r="L82" s="88"/>
       <c r="M82" s="102"/>
       <c r="N82" s="85" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O82" s="86"/>
     </row>
@@ -6586,7 +6596,7 @@
       </c>
       <c r="L84" s="46"/>
       <c r="M84" s="85" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -7342,25 +7352,25 @@
     </row>
     <row r="107" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A107" s="83" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B107" s="84" t="s">
         <v>448</v>
       </c>
       <c r="C107" s="80" t="s">
+        <v>609</v>
+      </c>
+      <c r="D107" s="81" t="s">
         <v>610</v>
       </c>
-      <c r="D107" s="81" t="s">
+      <c r="E107" s="92" t="s">
         <v>611</v>
-      </c>
-      <c r="E107" s="92" t="s">
-        <v>612</v>
       </c>
       <c r="F107" s="80" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="82" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H107" s="80" t="s">
         <v>265</v>
@@ -7470,7 +7480,7 @@
       </c>
       <c r="L110" s="46"/>
       <c r="N110" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="O110" s="59" t="s">
         <v>235</v>
@@ -7506,7 +7516,7 @@
       </c>
       <c r="L111" s="46"/>
       <c r="N111" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="O111" s="59" t="s">
         <v>235</v>
@@ -7542,7 +7552,7 @@
       </c>
       <c r="L112" s="46"/>
       <c r="N112" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="O112" s="59" t="s">
         <v>235</v>
@@ -7578,7 +7588,7 @@
       </c>
       <c r="L113" s="46"/>
       <c r="N113" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="O113" s="59" t="s">
         <v>235</v>
@@ -7614,7 +7624,7 @@
       </c>
       <c r="L114" s="46"/>
       <c r="N114" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="O114" s="59" t="s">
         <v>235</v>
@@ -7718,7 +7728,7 @@
       </c>
       <c r="L117" s="46"/>
       <c r="M117" s="102" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -7751,7 +7761,7 @@
       </c>
       <c r="L118" s="46"/>
       <c r="M118" s="102" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="153" x14ac:dyDescent="0.2">
@@ -7774,7 +7784,7 @@
         <v>232</v>
       </c>
       <c r="G119" s="82" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H119" s="49" t="s">
         <v>265</v>
@@ -7934,13 +7944,13 @@
         <v>450</v>
       </c>
       <c r="C124" s="49" t="s">
-        <v>615</v>
+        <v>648</v>
       </c>
       <c r="D124" s="61" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E124" s="49" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F124" s="49" t="s">
         <v>232</v>
@@ -7962,7 +7972,7 @@
     </row>
     <row r="125" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A125" s="103" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B125" s="84" t="s">
         <v>450</v>
@@ -7990,7 +8000,7 @@
     </row>
     <row r="126" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A126" s="88" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B126" s="84" t="s">
         <v>449</v>
@@ -8018,7 +8028,7 @@
     </row>
     <row r="127" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A127" s="88" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B127" s="84" t="s">
         <v>448</v>
@@ -8046,7 +8056,7 @@
     </row>
     <row r="128" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A128" s="88" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B128" s="84" t="s">
         <v>450</v>

--- a/S-158-111/1.1.0/WD-158_111_1_1_0_20260930.xlsx
+++ b/S-158-111/1.1.0/WD-158_111_1_1_0_20260930.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\TWCWG\S-158-111\1.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D942AE84-7DF8-43DA-8525-0D9A7DE9EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB752B-869A-485B-9F95-CA28929A0802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" activeTab="1" xr2:uid="{D500D42E-56ED-44C2-B321-3F3845968AA3}"/>
   </bookViews>
   <sheets>
     <sheet name="S100ValiSpec metadata" sheetId="11" r:id="rId1"/>
     <sheet name="S-111" sheetId="14" r:id="rId2"/>
-    <sheet name="Legend+Tracking+Notes(Internal)" sheetId="19" r:id="rId3"/>
+    <sheet name="111_2021" sheetId="20" r:id="rId3"/>
+    <sheet name="Legend+Tracking+Notes(Internal)" sheetId="19" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S-111'!$B$1:$B$465</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S-111'!$B$1:$B$466</definedName>
     <definedName name="S101_Disposition">[1]Lists!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="673">
   <si>
     <t>Classification</t>
   </si>
@@ -2333,6 +2334,79 @@
       </rPr>
       <t>Feature exceeds size limit</t>
     </r>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Barycenter</t>
+  </si>
+  <si>
+    <t>LowerLeft</t>
+  </si>
+  <si>
+    <t>UpperRight</t>
+  </si>
+  <si>
+    <t>LowerRight</t>
+  </si>
+  <si>
+    <t>UpperLeft</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Definition (from S-100 Table 10c-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XMin, YMin (“Lower left”) corner (“Cell  origin”) </t>
+  </si>
+  <si>
+    <t>XMax, YMax (“Upper right”) corner</t>
+  </si>
+  <si>
+    <t>XMax, YMin (“Lower right”) corner</t>
+  </si>
+  <si>
+    <t>XMin, YMax (“Upper left”) corner</t>
+  </si>
+  <si>
+    <t>Note that the definitions of the codes indicating the corners are in terms of X and Y grid coordinates relative to the grid origin. (This means that in a grid with its X axis directed from east to west and Y axis from north to south the “lower left” corner is different from the “lower left” corner in a grid with X axis directed west to east and Y axis south to north.)</t>
+  </si>
+  <si>
+    <t>Centroid of cell</t>
+  </si>
+  <si>
+    <t>Prohibited as a value of dataOffsetCode in S-111 datasets</t>
+  </si>
+  <si>
+    <t>See S-100 Table 10c-10 and sheet 111_2021 for enumeration codes and labels. Prohibited values may be used in defining the HDF5 enumeration type but must not be encoded as values of attribute dataOffsetCode</t>
+  </si>
+  <si>
+    <t>111_2026</t>
+  </si>
+  <si>
+    <t>Axis name error</t>
+  </si>
+  <si>
+    <t>Axes listed in axisNames are not latitude/longitude or northing/easting</t>
+  </si>
+  <si>
+    <t>Amend axisNames dataseet</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>Case-sensitive check.
+Validate combination too, e.g., latitude must be accompanied by longitude..</t>
+  </si>
+  <si>
+    <t>May require visual inspection</t>
   </si>
 </sst>
 </file>
@@ -2706,7 +2780,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2941,6 +3015,12 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2953,17 +3033,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3349,14 +3426,14 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="101"/>
       <c r="H2" s="7"/>
     </row>
     <row r="3" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,7 +3559,7 @@
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="98" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -3496,7 +3573,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="96"/>
+      <c r="B14" s="98"/>
       <c r="C14" s="29"/>
       <c r="D14" s="27"/>
       <c r="E14" s="30"/>
@@ -3504,7 +3581,7 @@
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="96"/>
+      <c r="B15" s="98"/>
       <c r="C15" s="32"/>
       <c r="D15" s="27"/>
       <c r="E15" s="28"/>
@@ -3512,7 +3589,7 @@
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="96"/>
+      <c r="B16" s="98"/>
       <c r="C16" s="22"/>
       <c r="D16" s="8"/>
       <c r="E16" s="21"/>
@@ -3520,7 +3597,7 @@
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="96"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="23"/>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
@@ -3528,7 +3605,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="96"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="13"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -3564,7 +3641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3229863E-76E8-4615-9B5D-DE44E34EF947}">
-  <dimension ref="A1:P465"/>
+  <dimension ref="A1:P466"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="46" customWidth="1"/>
@@ -3579,7 +3656,7 @@
     <col min="10" max="10" width="8.28515625" style="46" customWidth="1"/>
     <col min="11" max="11" width="8" style="46" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" style="36" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="101" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" style="2" customWidth="1"/>
     <col min="14" max="14" width="31.140625" style="2" customWidth="1"/>
     <col min="15" max="15" width="16.42578125" style="59" customWidth="1"/>
     <col min="16" max="16384" width="8.7109375" style="1"/>
@@ -3622,7 +3699,7 @@
       <c r="L1" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="M1" s="100" t="s">
+      <c r="M1" s="96" t="s">
         <v>635</v>
       </c>
       <c r="N1" s="78" t="s">
@@ -3702,7 +3779,7 @@
       </c>
       <c r="J3" s="36"/>
       <c r="K3" s="36"/>
-      <c r="M3" s="102" t="s">
+      <c r="M3" s="85" t="s">
         <v>636</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -3777,7 +3854,7 @@
       </c>
       <c r="J5" s="36"/>
       <c r="K5" s="36"/>
-      <c r="M5" s="102" t="s">
+      <c r="M5" s="85" t="s">
         <v>638</v>
       </c>
       <c r="N5" s="42" t="s">
@@ -4277,7 +4354,7 @@
         <v>447</v>
       </c>
       <c r="L18" s="83"/>
-      <c r="M18" s="102"/>
+      <c r="M18" s="85"/>
       <c r="N18" s="85" t="s">
         <v>644</v>
       </c>
@@ -4738,59 +4815,54 @@
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="36" t="s">
+    <row r="32" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="83" t="s">
+        <v>666</v>
+      </c>
+      <c r="B32" s="84" t="s">
+        <v>448</v>
+      </c>
+      <c r="C32" s="92" t="s">
+        <v>667</v>
+      </c>
+      <c r="D32" s="103" t="s">
+        <v>668</v>
+      </c>
+      <c r="E32" s="80" t="s">
+        <v>669</v>
+      </c>
+      <c r="F32" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="82" t="s">
+        <v>670</v>
+      </c>
+      <c r="H32" s="92"/>
+      <c r="I32" s="83" t="s">
+        <v>447</v>
+      </c>
+      <c r="J32" s="88"/>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="104" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="36" t="s">
         <v>481</v>
-      </c>
-      <c r="B32" s="60" t="s">
-        <v>448</v>
-      </c>
-      <c r="C32" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G32" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="H32" s="67" t="s">
-        <v>265</v>
-      </c>
-      <c r="I32" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="L32" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="36" t="s">
-        <v>482</v>
       </c>
       <c r="B33" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="D33" s="68" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="67" t="s">
-        <v>291</v>
+        <v>49</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>159</v>
       </c>
       <c r="F33" s="49" t="s">
         <v>232</v>
@@ -4816,53 +4888,57 @@
     </row>
     <row r="34" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="36" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="D34" s="68" t="s">
-        <v>393</v>
+        <v>50</v>
       </c>
       <c r="E34" s="67" t="s">
-        <v>160</v>
+        <v>291</v>
       </c>
       <c r="F34" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H34" s="67" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I34" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="L34" s="46"/>
-      <c r="N34" s="85"/>
+      <c r="L34" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="O34" s="59" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B35" s="60" t="s">
         <v>449</v>
       </c>
-      <c r="C35" s="49" t="s">
-        <v>298</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>161</v>
+      <c r="C35" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>393</v>
+      </c>
+      <c r="E35" s="67" t="s">
+        <v>160</v>
       </c>
       <c r="F35" s="49" t="s">
         <v>232</v>
@@ -4870,8 +4946,8 @@
       <c r="G35" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="H35" s="49" t="s">
-        <v>265</v>
+      <c r="H35" s="67" t="s">
+        <v>266</v>
       </c>
       <c r="I35" s="36" t="s">
         <v>277</v>
@@ -4879,24 +4955,24 @@
       <c r="L35" s="46"/>
       <c r="N35" s="85"/>
       <c r="O35" s="59" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A36" s="36" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B36" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>47</v>
+        <v>298</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="F36" s="49" t="s">
         <v>232</v>
@@ -4905,7 +4981,7 @@
         <v>149</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I36" s="36" t="s">
         <v>277</v>
@@ -4916,21 +4992,21 @@
         <v>239</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="36" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B37" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="F37" s="49" t="s">
         <v>232</v>
@@ -4939,7 +5015,7 @@
         <v>149</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I37" s="36" t="s">
         <v>277</v>
@@ -4950,21 +5026,21 @@
         <v>239</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="114.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="36" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B38" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>130</v>
+        <v>381</v>
       </c>
       <c r="D38" s="61" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F38" s="49" t="s">
         <v>232</v>
@@ -4973,37 +5049,32 @@
         <v>149</v>
       </c>
       <c r="H38" s="49" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I38" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L38" s="46"/>
-      <c r="M38" s="102" t="s">
-        <v>645</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>646</v>
-      </c>
+      <c r="N38" s="85"/>
       <c r="O38" s="59" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A39" s="36" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B39" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="E39" s="49" t="s">
-        <v>321</v>
+        <v>163</v>
       </c>
       <c r="F39" s="49" t="s">
         <v>232</v>
@@ -5012,32 +5083,37 @@
         <v>149</v>
       </c>
       <c r="H39" s="49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="L39" s="46"/>
-      <c r="N39" s="85"/>
+      <c r="M39" s="85" t="s">
+        <v>645</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>646</v>
+      </c>
       <c r="O39" s="59" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A40" s="36" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>131</v>
+        <v>320</v>
       </c>
       <c r="D40" s="61" t="s">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="E40" s="49" t="s">
-        <v>164</v>
+        <v>321</v>
       </c>
       <c r="F40" s="49" t="s">
         <v>232</v>
@@ -5045,286 +5121,288 @@
       <c r="G40" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="H40" s="67" t="s">
-        <v>267</v>
+      <c r="H40" s="49" t="s">
+        <v>266</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="L40" s="46"/>
+      <c r="M40" s="85" t="s">
+        <v>665</v>
+      </c>
+      <c r="N40" s="85"/>
       <c r="O40" s="59" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A41" s="36" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B41" s="60" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>372</v>
-      </c>
-      <c r="D41" s="63" t="s">
-        <v>373</v>
+        <v>131</v>
+      </c>
+      <c r="D41" s="61" t="s">
+        <v>398</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>374</v>
+        <v>164</v>
       </c>
       <c r="F41" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G41" s="52" t="s">
-        <v>355</v>
-      </c>
-      <c r="H41" s="49" t="s">
-        <v>265</v>
+        <v>149</v>
+      </c>
+      <c r="H41" s="67" t="s">
+        <v>267</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="N41" s="2" t="s">
-        <v>356</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="L41" s="46"/>
       <c r="O41" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="114.75" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A42" s="36" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" s="61" t="s">
-        <v>35</v>
+        <v>372</v>
+      </c>
+      <c r="D42" s="63" t="s">
+        <v>373</v>
       </c>
       <c r="E42" s="49" t="s">
-        <v>60</v>
+        <v>374</v>
       </c>
       <c r="F42" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G42" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="H42" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="I42" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="N42" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O42" s="59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A43" s="36" t="s">
+        <v>491</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>450</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="H42" s="67" t="s">
+      <c r="H43" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="I42" s="36" t="s">
+      <c r="I43" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="L42" s="46"/>
-      <c r="N42" s="2" t="s">
+      <c r="L43" s="46"/>
+      <c r="N43" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="O42" s="59" t="s">
+      <c r="O43" s="59" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A43" s="83" t="s">
+    <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A44" s="83" t="s">
         <v>492</v>
       </c>
-      <c r="B43" s="60" t="s">
+      <c r="B44" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="49" t="s">
+      <c r="C44" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="61" t="s">
+      <c r="D44" s="61" t="s">
         <v>279</v>
       </c>
-      <c r="E43" s="49" t="s">
+      <c r="E44" s="49" t="s">
         <v>300</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F44" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="G43" s="52" t="s">
+      <c r="G44" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="H43" s="49" t="s">
+      <c r="H44" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="I43" s="83" t="s">
+      <c r="I44" s="83" t="s">
         <v>277</v>
       </c>
-      <c r="K43" s="88" t="s">
+      <c r="K44" s="88" t="s">
         <v>447</v>
       </c>
-      <c r="L43" s="46"/>
-      <c r="N43" s="85" t="s">
+      <c r="L44" s="46"/>
+      <c r="N44" s="85" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="36" t="s">
+    <row r="45" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="36" t="s">
         <v>493</v>
-      </c>
-      <c r="B44" s="60" t="s">
-        <v>449</v>
-      </c>
-      <c r="C44" s="49" t="s">
-        <v>399</v>
-      </c>
-      <c r="D44" s="61" t="s">
-        <v>581</v>
-      </c>
-      <c r="E44" s="49" t="s">
-        <v>400</v>
-      </c>
-      <c r="F44" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G44" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="I44" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="J44" s="83"/>
-      <c r="K44" s="36"/>
-      <c r="N44" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="O44" s="59" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="178.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="36" t="s">
-        <v>494</v>
       </c>
       <c r="B45" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="D45" s="61" t="s">
-        <v>401</v>
+        <v>581</v>
       </c>
       <c r="E45" s="49" t="s">
-        <v>53</v>
+        <v>400</v>
       </c>
       <c r="F45" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G45" s="52" t="s">
-        <v>301</v>
+        <v>118</v>
       </c>
       <c r="H45" s="49" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I45" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="J45" s="36"/>
+      <c r="J45" s="83"/>
       <c r="K45" s="36"/>
       <c r="N45" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="O45" s="59" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="178.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="B46" s="60" t="s">
+        <v>449</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="61" t="s">
+        <v>401</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G46" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="H46" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="N46" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="O45" s="59" t="s">
+      <c r="O46" s="59" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A46" s="83" t="s">
+    <row r="47" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A47" s="83" t="s">
         <v>573</v>
       </c>
-      <c r="B46" s="84" t="s">
+      <c r="B47" s="84" t="s">
         <v>449</v>
       </c>
-      <c r="C46" s="80" t="s">
+      <c r="C47" s="80" t="s">
         <v>571</v>
       </c>
-      <c r="D46" s="81" t="s">
+      <c r="D47" s="81" t="s">
         <v>603</v>
       </c>
-      <c r="E46" s="80" t="s">
+      <c r="E47" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="F46" s="80" t="s">
+      <c r="F47" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="G46" s="82" t="s">
+      <c r="G47" s="82" t="s">
         <v>263</v>
       </c>
-      <c r="H46" s="80" t="s">
+      <c r="H47" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="I46" s="83" t="s">
+      <c r="I47" s="83" t="s">
         <v>447</v>
       </c>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="102" t="s">
+      <c r="J47" s="83"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="83"/>
+      <c r="M47" s="85" t="s">
         <v>647</v>
       </c>
-      <c r="N46" s="85"/>
-      <c r="O46" s="86"/>
-    </row>
-    <row r="47" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="36" t="s">
-        <v>495</v>
-      </c>
-      <c r="B47" s="60" t="s">
-        <v>449</v>
-      </c>
-      <c r="C47" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="D47" s="63" t="s">
-        <v>403</v>
-      </c>
-      <c r="E47" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F47" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G47" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H47" s="62" t="s">
-        <v>265</v>
-      </c>
-      <c r="I47" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
       <c r="N47" s="85"/>
-      <c r="O47" s="59" t="s">
-        <v>242</v>
-      </c>
+      <c r="O47" s="86"/>
     </row>
     <row r="48" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A48" s="36" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B48" s="60" t="s">
-        <v>448</v>
-      </c>
-      <c r="C48" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="D48" s="61" t="s">
-        <v>404</v>
-      </c>
-      <c r="E48" s="49" t="s">
+        <v>449</v>
+      </c>
+      <c r="C48" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="63" t="s">
+        <v>403</v>
+      </c>
+      <c r="E48" s="62" t="s">
         <v>56</v>
       </c>
       <c r="F48" s="49" t="s">
@@ -5333,7 +5411,7 @@
       <c r="G48" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H48" s="49" t="s">
+      <c r="H48" s="62" t="s">
         <v>265</v>
       </c>
       <c r="I48" s="36" t="s">
@@ -5346,21 +5424,21 @@
         <v>242</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A49" s="36" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B49" s="60" t="s">
-        <v>449</v>
-      </c>
-      <c r="C49" s="69" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="70" t="s">
-        <v>405</v>
-      </c>
-      <c r="E49" s="69" t="s">
-        <v>165</v>
+        <v>448</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="F49" s="49" t="s">
         <v>232</v>
@@ -5381,21 +5459,21 @@
         <v>242</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A50" s="36" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B50" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C50" s="69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D50" s="70" t="s">
-        <v>114</v>
+        <v>405</v>
       </c>
       <c r="E50" s="69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F50" s="49" t="s">
         <v>232</v>
@@ -5404,32 +5482,33 @@
         <v>118</v>
       </c>
       <c r="H50" s="49" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I50" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J50" s="36"/>
       <c r="K50" s="36"/>
+      <c r="N50" s="85"/>
       <c r="O50" s="59" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A51" s="36" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B51" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C51" s="69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D51" s="70" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E51" s="69" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="F51" s="49" t="s">
         <v>232</v>
@@ -5438,30 +5517,29 @@
         <v>118</v>
       </c>
       <c r="H51" s="49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I51" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J51" s="36"/>
       <c r="K51" s="36"/>
-      <c r="N51" s="85"/>
       <c r="O51" s="59" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A52" s="36" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B52" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C52" s="69" t="s">
-        <v>288</v>
+        <v>95</v>
       </c>
       <c r="D52" s="70" t="s">
-        <v>289</v>
+        <v>115</v>
       </c>
       <c r="E52" s="69" t="s">
         <v>56</v>
@@ -5473,32 +5551,30 @@
         <v>118</v>
       </c>
       <c r="H52" s="49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="J52" s="36"/>
       <c r="K52" s="36"/>
-      <c r="N52" s="2" t="s">
-        <v>630</v>
-      </c>
+      <c r="N52" s="85"/>
       <c r="O52" s="59" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A53" s="36" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B53" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C53" s="69" t="s">
-        <v>96</v>
+        <v>288</v>
       </c>
       <c r="D53" s="70" t="s">
-        <v>406</v>
+        <v>289</v>
       </c>
       <c r="E53" s="69" t="s">
         <v>56</v>
@@ -5510,32 +5586,34 @@
         <v>118</v>
       </c>
       <c r="H53" s="49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="J53" s="36"/>
       <c r="K53" s="36"/>
-      <c r="N53" s="85"/>
+      <c r="N53" s="2" t="s">
+        <v>630</v>
+      </c>
       <c r="O53" s="59" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A54" s="36" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B54" s="60" t="s">
         <v>449</v>
       </c>
-      <c r="C54" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="E54" s="49" t="s">
+      <c r="C54" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="70" t="s">
+        <v>406</v>
+      </c>
+      <c r="E54" s="69" t="s">
         <v>56</v>
       </c>
       <c r="F54" s="49" t="s">
@@ -5557,18 +5635,18 @@
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A55" s="36" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B55" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" s="61" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E55" s="49" t="s">
         <v>56</v>
@@ -5592,21 +5670,21 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A56" s="36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B56" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="C56" s="69" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" s="70" t="s">
-        <v>409</v>
-      </c>
-      <c r="E56" s="69" t="s">
-        <v>55</v>
+        <v>449</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="61" t="s">
+        <v>408</v>
+      </c>
+      <c r="E56" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="F56" s="49" t="s">
         <v>232</v>
@@ -5614,36 +5692,34 @@
       <c r="G56" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H56" s="69" t="s">
-        <v>267</v>
+      <c r="H56" s="49" t="s">
+        <v>265</v>
       </c>
       <c r="I56" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J56" s="36"/>
       <c r="K56" s="36"/>
-      <c r="N56" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="N56" s="85"/>
       <c r="O56" s="59" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A57" s="36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B57" s="60" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C57" s="69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D57" s="70" t="s">
-        <v>410</v>
-      </c>
-      <c r="E57" s="49" t="s">
-        <v>56</v>
+        <v>409</v>
+      </c>
+      <c r="E57" s="69" t="s">
+        <v>55</v>
       </c>
       <c r="F57" s="49" t="s">
         <v>232</v>
@@ -5652,35 +5728,35 @@
         <v>118</v>
       </c>
       <c r="H57" s="69" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I57" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J57" s="36"/>
       <c r="K57" s="36"/>
-      <c r="N57" s="95" t="s">
-        <v>631</v>
+      <c r="N57" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="O57" s="59" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" s="36" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B58" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C58" s="69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D58" s="70" t="s">
-        <v>411</v>
-      </c>
-      <c r="E58" s="69" t="s">
-        <v>57</v>
+        <v>410</v>
+      </c>
+      <c r="E58" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="F58" s="49" t="s">
         <v>232</v>
@@ -5689,35 +5765,35 @@
         <v>118</v>
       </c>
       <c r="H58" s="69" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I58" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J58" s="36"/>
       <c r="K58" s="36"/>
-      <c r="N58" s="2" t="s">
-        <v>256</v>
+      <c r="N58" s="95" t="s">
+        <v>631</v>
       </c>
       <c r="O58" s="59" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A59" s="36" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B59" s="60" t="s">
         <v>450</v>
       </c>
-      <c r="C59" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" s="61" t="s">
-        <v>412</v>
-      </c>
-      <c r="E59" s="49" t="s">
-        <v>58</v>
+      <c r="C59" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="70" t="s">
+        <v>411</v>
+      </c>
+      <c r="E59" s="69" t="s">
+        <v>57</v>
       </c>
       <c r="F59" s="49" t="s">
         <v>232</v>
@@ -5725,7 +5801,7 @@
       <c r="G59" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H59" s="49" t="s">
+      <c r="H59" s="69" t="s">
         <v>267</v>
       </c>
       <c r="I59" s="36" t="s">
@@ -5734,27 +5810,27 @@
       <c r="J59" s="36"/>
       <c r="K59" s="36"/>
       <c r="N59" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O59" s="59" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A60" s="36" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B60" s="60" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D60" s="61" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E60" s="49" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F60" s="49" t="s">
         <v>232</v>
@@ -5763,33 +5839,35 @@
         <v>118</v>
       </c>
       <c r="H60" s="49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I60" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J60" s="36"/>
       <c r="K60" s="36"/>
-      <c r="N60" s="85"/>
+      <c r="N60" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="O60" s="59" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A61" s="36" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B61" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" s="61" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F61" s="49" t="s">
         <v>232</v>
@@ -5797,36 +5875,34 @@
       <c r="G61" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H61" s="67" t="s">
-        <v>267</v>
+      <c r="H61" s="49" t="s">
+        <v>265</v>
       </c>
       <c r="I61" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J61" s="36"/>
       <c r="K61" s="36"/>
-      <c r="N61" s="2" t="s">
-        <v>580</v>
-      </c>
+      <c r="N61" s="85"/>
       <c r="O61" s="59" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A62" s="36" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B62" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F62" s="49" t="s">
         <v>232</v>
@@ -5835,29 +5911,32 @@
         <v>118</v>
       </c>
       <c r="H62" s="67" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I62" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="L62" s="46"/>
-      <c r="N62" s="85"/>
+      <c r="J62" s="36"/>
+      <c r="K62" s="36"/>
+      <c r="N62" s="2" t="s">
+        <v>580</v>
+      </c>
       <c r="O62" s="59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A63" s="36" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B63" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E63" s="49" t="s">
         <v>56</v>
@@ -5882,7 +5961,7 @@
     </row>
     <row r="64" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A64" s="36" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B64" s="60" t="s">
         <v>449</v>
@@ -5891,7 +5970,7 @@
         <v>106</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>322</v>
+        <v>416</v>
       </c>
       <c r="E64" s="49" t="s">
         <v>56</v>
@@ -5906,7 +5985,7 @@
         <v>265</v>
       </c>
       <c r="I64" s="36" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L64" s="46"/>
       <c r="N64" s="85"/>
@@ -5914,21 +5993,21 @@
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B65" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D65" s="61" t="s">
-        <v>116</v>
+        <v>322</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="F65" s="49" t="s">
         <v>232</v>
@@ -5940,26 +6019,29 @@
         <v>265</v>
       </c>
       <c r="I65" s="36" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="L65" s="46"/>
       <c r="N65" s="85"/>
-    </row>
-    <row r="66" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="O65" s="59" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A66" s="36" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B66" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>417</v>
+        <v>107</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>418</v>
-      </c>
-      <c r="E66" s="67" t="s">
-        <v>54</v>
+        <v>116</v>
+      </c>
+      <c r="E66" s="49" t="s">
+        <v>167</v>
       </c>
       <c r="F66" s="49" t="s">
         <v>232</v>
@@ -5967,7 +6049,7 @@
       <c r="G66" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H66" s="49" t="s">
+      <c r="H66" s="67" t="s">
         <v>265</v>
       </c>
       <c r="I66" s="36" t="s">
@@ -5978,136 +6060,129 @@
     </row>
     <row r="67" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A67" s="36" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B67" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>375</v>
-      </c>
-      <c r="D67" s="63" t="s">
-        <v>376</v>
-      </c>
-      <c r="E67" s="49" t="s">
-        <v>377</v>
+        <v>417</v>
+      </c>
+      <c r="D67" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="E67" s="67" t="s">
+        <v>54</v>
       </c>
       <c r="F67" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G67" s="52" t="s">
-        <v>355</v>
+        <v>118</v>
       </c>
       <c r="H67" s="49" t="s">
         <v>265</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="J67" s="36"/>
-      <c r="K67" s="36"/>
-      <c r="N67" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="O67" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="165.75" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+      <c r="L67" s="46"/>
+      <c r="N67" s="85"/>
+    </row>
+    <row r="68" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A68" s="36" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="D68" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="67" t="s">
-        <v>60</v>
+        <v>375</v>
+      </c>
+      <c r="D68" s="63" t="s">
+        <v>376</v>
+      </c>
+      <c r="E68" s="49" t="s">
+        <v>377</v>
       </c>
       <c r="F68" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G68" s="52" t="s">
-        <v>261</v>
+        <v>355</v>
       </c>
       <c r="H68" s="49" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="L68" s="46"/>
+        <v>290</v>
+      </c>
+      <c r="J68" s="36"/>
+      <c r="K68" s="36"/>
       <c r="N68" s="2" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="O68" s="59" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A69" s="36" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B69" s="60" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C69" s="49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D69" s="61" t="s">
-        <v>292</v>
+        <v>35</v>
       </c>
       <c r="E69" s="67" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="F69" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G69" s="52" t="s">
-        <v>88</v>
+        <v>261</v>
       </c>
       <c r="H69" s="49" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="I69" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="L69" s="36" t="b">
-        <v>1</v>
-      </c>
+      <c r="L69" s="46"/>
       <c r="N69" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O69" s="59" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="153" x14ac:dyDescent="0.2">
       <c r="A70" s="36" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B70" s="60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C70" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D70" s="61" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="E70" s="67" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="F70" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G70" s="52" t="s">
-        <v>260</v>
+        <v>88</v>
       </c>
       <c r="H70" s="49" t="s">
         <v>265</v>
@@ -6115,33 +6190,37 @@
       <c r="I70" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="L70" s="46"/>
-      <c r="N70" s="85"/>
+      <c r="L70" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="O70" s="59" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" s="36" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B71" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C71" s="49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D71" s="61" t="s">
-        <v>419</v>
+        <v>117</v>
       </c>
       <c r="E71" s="67" t="s">
-        <v>420</v>
+        <v>61</v>
       </c>
       <c r="F71" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G71" s="52" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="H71" s="49" t="s">
         <v>265</v>
@@ -6152,30 +6231,30 @@
       <c r="L71" s="46"/>
       <c r="N71" s="85"/>
       <c r="O71" s="59" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" s="36" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B72" s="60" t="s">
         <v>450</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D72" s="61" t="s">
-        <v>293</v>
+        <v>419</v>
       </c>
       <c r="E72" s="67" t="s">
-        <v>169</v>
+        <v>420</v>
       </c>
       <c r="F72" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G72" s="52" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H72" s="49" t="s">
         <v>265</v>
@@ -6189,90 +6268,88 @@
         <v>245</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A73" s="83" t="s">
+    <row r="73" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A73" s="36" t="s">
+        <v>520</v>
+      </c>
+      <c r="B73" s="60" t="s">
+        <v>450</v>
+      </c>
+      <c r="C73" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" s="61" t="s">
+        <v>293</v>
+      </c>
+      <c r="E73" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="F73" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G73" s="52" t="s">
+        <v>306</v>
+      </c>
+      <c r="H73" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="I73" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="L73" s="46"/>
+      <c r="N73" s="85"/>
+      <c r="O73" s="59" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A74" s="83" t="s">
         <v>521</v>
       </c>
-      <c r="B73" s="84" t="s">
+      <c r="B74" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="80" t="s">
+      <c r="C74" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="D73" s="81" t="s">
+      <c r="D74" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="E73" s="92" t="s">
+      <c r="E74" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F73" s="80"/>
-      <c r="G73" s="82"/>
-      <c r="H73" s="80" t="s">
+      <c r="F74" s="80"/>
+      <c r="G74" s="82"/>
+      <c r="H74" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="I73" s="83" t="s">
+      <c r="I74" s="83" t="s">
         <v>277</v>
       </c>
-      <c r="J73" s="88"/>
-      <c r="K73" s="88" t="s">
+      <c r="J74" s="88"/>
+      <c r="K74" s="88" t="s">
         <v>447</v>
       </c>
-      <c r="L73" s="88"/>
-      <c r="N73" s="2" t="s">
+      <c r="L74" s="88"/>
+      <c r="N74" s="2" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A74" s="36" t="s">
+    <row r="75" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="36" t="s">
         <v>522</v>
-      </c>
-      <c r="B74" s="60" t="s">
-        <v>448</v>
-      </c>
-      <c r="C74" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="D74" s="61" t="s">
-        <v>421</v>
-      </c>
-      <c r="E74" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="F74" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G74" s="52" t="s">
-        <v>307</v>
-      </c>
-      <c r="H74" s="67" t="s">
-        <v>265</v>
-      </c>
-      <c r="I74" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="L74" s="46"/>
-      <c r="N74" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O74" s="59" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A75" s="36" t="s">
-        <v>523</v>
       </c>
       <c r="B75" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C75" s="49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D75" s="61" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E75" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F75" s="49" t="s">
         <v>232</v>
@@ -6287,32 +6364,34 @@
         <v>277</v>
       </c>
       <c r="L75" s="46"/>
-      <c r="N75" s="85"/>
+      <c r="N75" s="2" t="s">
+        <v>308</v>
+      </c>
       <c r="O75" s="59" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A76" s="36" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B76" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C76" s="49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D76" s="61" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E76" s="49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F76" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G76" s="52" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H76" s="67" t="s">
         <v>265</v>
@@ -6323,24 +6402,24 @@
       <c r="L76" s="46"/>
       <c r="N76" s="85"/>
       <c r="O76" s="59" t="s">
-        <v>247</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A77" s="36" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B77" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C77" s="49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D77" s="61" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E77" s="49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" s="49" t="s">
         <v>232</v>
@@ -6348,32 +6427,30 @@
       <c r="G77" s="52" t="s">
         <v>310</v>
       </c>
-      <c r="H77" s="49" t="s">
+      <c r="H77" s="67" t="s">
         <v>265</v>
       </c>
       <c r="I77" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L77" s="46"/>
-      <c r="N77" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="N77" s="85"/>
       <c r="O77" s="59" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="36" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B78" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C78" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D78" s="61" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E78" s="49" t="s">
         <v>145</v>
@@ -6382,32 +6459,34 @@
         <v>232</v>
       </c>
       <c r="G78" s="52" t="s">
-        <v>148</v>
+        <v>310</v>
       </c>
       <c r="H78" s="49" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I78" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L78" s="46"/>
-      <c r="N78" s="85"/>
+      <c r="N78" s="2" t="s">
+        <v>258</v>
+      </c>
       <c r="O78" s="59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="36" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B79" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D79" s="61" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E79" s="49" t="s">
         <v>145</v>
@@ -6430,18 +6509,18 @@
         <v>246</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A80" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B80" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C80" s="49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D80" s="61" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E80" s="49" t="s">
         <v>145</v>
@@ -6464,190 +6543,190 @@
         <v>246</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="36" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C81" s="49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D81" s="61" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E81" s="49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F81" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="G81" s="52"/>
+      <c r="G81" s="52" t="s">
+        <v>148</v>
+      </c>
       <c r="H81" s="49" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="I81" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="K81" s="88" t="s">
+      <c r="L81" s="46"/>
+      <c r="N81" s="85"/>
+      <c r="O81" s="59" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A82" s="36" t="s">
+        <v>529</v>
+      </c>
+      <c r="B82" s="60" t="s">
+        <v>449</v>
+      </c>
+      <c r="C82" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="D82" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="E82" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="F82" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G82" s="52"/>
+      <c r="H82" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="I82" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="K82" s="88" t="s">
         <v>447</v>
       </c>
-      <c r="L81" s="46"/>
-      <c r="N81" s="2" t="s">
+      <c r="L82" s="46"/>
+      <c r="N82" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="O81" s="59" t="s">
+      <c r="O82" s="59" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="83" t="s">
+    <row r="83" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="B82" s="84" t="s">
+      <c r="B83" s="84" t="s">
         <v>449</v>
       </c>
-      <c r="C82" s="80" t="s">
+      <c r="C83" s="80" t="s">
         <v>606</v>
       </c>
-      <c r="D82" s="81" t="s">
+      <c r="D83" s="81" t="s">
         <v>607</v>
       </c>
-      <c r="E82" s="80" t="s">
+      <c r="E83" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="F82" s="80" t="s">
+      <c r="F83" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="G82" s="82" t="s">
+      <c r="G83" s="82" t="s">
         <v>634</v>
       </c>
-      <c r="H82" s="80"/>
-      <c r="I82" s="83" t="s">
+      <c r="H83" s="80"/>
+      <c r="I83" s="83" t="s">
         <v>447</v>
       </c>
-      <c r="J82" s="88"/>
-      <c r="K82" s="88"/>
-      <c r="L82" s="88"/>
-      <c r="M82" s="102"/>
-      <c r="N82" s="85" t="s">
+      <c r="J83" s="88"/>
+      <c r="K83" s="88"/>
+      <c r="L83" s="88"/>
+      <c r="M83" s="85"/>
+      <c r="N83" s="85" t="s">
         <v>608</v>
       </c>
-      <c r="O82" s="86"/>
-    </row>
-    <row r="83" spans="1:16" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="36" t="s">
+      <c r="O83" s="86"/>
+    </row>
+    <row r="84" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A84" s="36" t="s">
         <v>530</v>
       </c>
-      <c r="B83" s="60" t="s">
+      <c r="B84" s="60" t="s">
         <v>450</v>
       </c>
-      <c r="C83" s="49" t="s">
+      <c r="C84" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="D83" s="61" t="s">
+      <c r="D84" s="61" t="s">
         <v>429</v>
       </c>
-      <c r="E83" s="49" t="s">
+      <c r="E84" s="49" t="s">
         <v>60</v>
-      </c>
-      <c r="F83" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G83" s="52" t="s">
-        <v>307</v>
-      </c>
-      <c r="H83" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="I83" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="L83" s="46"/>
-    </row>
-    <row r="84" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="36" t="s">
-        <v>531</v>
-      </c>
-      <c r="B84" s="60" t="s">
-        <v>449</v>
-      </c>
-      <c r="C84" s="49" t="s">
-        <v>179</v>
-      </c>
-      <c r="D84" s="61" t="s">
-        <v>430</v>
-      </c>
-      <c r="E84" s="49" t="s">
-        <v>147</v>
       </c>
       <c r="F84" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="G84" s="82" t="s">
-        <v>43</v>
+      <c r="G84" s="52" t="s">
+        <v>307</v>
       </c>
       <c r="H84" s="49" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I84" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L84" s="46"/>
-      <c r="M84" s="85" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A85" s="36" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B85" s="60" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C85" s="49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D85" s="61" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E85" s="49" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="F85" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="G85" s="52" t="s">
-        <v>432</v>
+      <c r="G85" s="82" t="s">
+        <v>43</v>
       </c>
       <c r="H85" s="49" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I85" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L85" s="46"/>
-      <c r="N85" s="85"/>
-      <c r="O85" s="59" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="M85" s="85" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="36" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B86" s="60" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C86" s="49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D86" s="61" t="s">
-        <v>196</v>
+        <v>431</v>
       </c>
       <c r="E86" s="49" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="F86" s="49" t="s">
         <v>232</v>
@@ -6656,68 +6735,68 @@
         <v>432</v>
       </c>
       <c r="H86" s="49" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="I86" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L86" s="46"/>
-      <c r="N86" s="2" t="s">
-        <v>250</v>
-      </c>
+      <c r="N86" s="85"/>
       <c r="O86" s="59" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A87" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B87" s="60" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C87" s="49" t="s">
-        <v>327</v>
+        <v>181</v>
       </c>
       <c r="D87" s="61" t="s">
-        <v>328</v>
+        <v>196</v>
       </c>
       <c r="E87" s="49" t="s">
-        <v>329</v>
+        <v>202</v>
       </c>
       <c r="F87" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G87" s="52" t="s">
-        <v>326</v>
+        <v>432</v>
       </c>
       <c r="H87" s="49" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="I87" s="36" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="L87" s="46"/>
-      <c r="N87" s="85"/>
+      <c r="N87" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="O87" s="59" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="36" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B88" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D88" s="61" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E88" s="49" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F88" s="49" t="s">
         <v>232</v>
@@ -6737,21 +6816,21 @@
         <v>311</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A89" s="36" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B89" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C89" s="49" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D89" s="61" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E89" s="49" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F89" s="49" t="s">
         <v>232</v>
@@ -6771,21 +6850,21 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A90" s="36" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B90" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D90" s="61" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E90" s="49" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F90" s="49" t="s">
         <v>232</v>
@@ -6805,21 +6884,21 @@
         <v>311</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A91" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B91" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C91" s="49" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D91" s="61" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E91" s="49" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F91" s="49" t="s">
         <v>232</v>
@@ -6839,21 +6918,21 @@
         <v>311</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A92" s="36" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B92" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C92" s="49" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D92" s="61" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E92" s="49" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F92" s="49" t="s">
         <v>232</v>
@@ -6873,21 +6952,21 @@
         <v>311</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A93" s="36" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B93" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C93" s="49" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D93" s="61" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E93" s="49" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F93" s="49" t="s">
         <v>232</v>
@@ -6907,21 +6986,21 @@
         <v>311</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A94" s="36" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B94" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C94" s="49" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D94" s="61" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E94" s="49" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F94" s="49" t="s">
         <v>232</v>
@@ -6938,24 +7017,24 @@
       <c r="L94" s="46"/>
       <c r="N94" s="85"/>
       <c r="O94" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A95" s="36" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B95" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C95" s="49" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D95" s="61" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E95" s="49" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F95" s="49" t="s">
         <v>232</v>
@@ -6975,21 +7054,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A96" s="36" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B96" s="60" t="s">
         <v>449</v>
       </c>
       <c r="C96" s="49" t="s">
-        <v>107</v>
+        <v>351</v>
       </c>
       <c r="D96" s="61" t="s">
-        <v>116</v>
+        <v>352</v>
       </c>
       <c r="E96" s="49" t="s">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="F96" s="49" t="s">
         <v>232</v>
@@ -6997,7 +7076,7 @@
       <c r="G96" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="H96" s="67" t="s">
+      <c r="H96" s="49" t="s">
         <v>265</v>
       </c>
       <c r="I96" s="36" t="s">
@@ -7008,23 +7087,22 @@
       <c r="O96" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="P96" s="59"/>
-    </row>
-    <row r="97" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A97" s="36" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B97" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="C97" s="67" t="s">
-        <v>126</v>
-      </c>
-      <c r="D97" s="68" t="s">
-        <v>359</v>
-      </c>
-      <c r="E97" s="67" t="s">
-        <v>156</v>
+        <v>449</v>
+      </c>
+      <c r="C97" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="E97" s="49" t="s">
+        <v>167</v>
       </c>
       <c r="F97" s="49" t="s">
         <v>232</v>
@@ -7043,22 +7121,23 @@
       <c r="O97" s="59" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="P97" s="59"/>
+    </row>
+    <row r="98" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="36" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B98" s="60" t="s">
         <v>450</v>
       </c>
       <c r="C98" s="67" t="s">
-        <v>360</v>
+        <v>126</v>
       </c>
       <c r="D98" s="68" t="s">
-        <v>361</v>
-      </c>
-      <c r="E98" s="49" t="s">
-        <v>157</v>
+        <v>359</v>
+      </c>
+      <c r="E98" s="67" t="s">
+        <v>156</v>
       </c>
       <c r="F98" s="49" t="s">
         <v>232</v>
@@ -7066,7 +7145,7 @@
       <c r="G98" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="H98" s="49" t="s">
+      <c r="H98" s="67" t="s">
         <v>265</v>
       </c>
       <c r="I98" s="36" t="s">
@@ -7078,61 +7157,61 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A99" s="36" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B99" s="60" t="s">
-        <v>448</v>
-      </c>
-      <c r="C99" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="D99" s="61" t="s">
-        <v>197</v>
+        <v>450</v>
+      </c>
+      <c r="C99" s="67" t="s">
+        <v>360</v>
+      </c>
+      <c r="D99" s="68" t="s">
+        <v>361</v>
       </c>
       <c r="E99" s="49" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="F99" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G99" s="52" t="s">
-        <v>88</v>
+        <v>326</v>
       </c>
       <c r="H99" s="49" t="s">
         <v>265</v>
       </c>
       <c r="I99" s="36" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="L99" s="46"/>
       <c r="N99" s="85"/>
       <c r="O99" s="59" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A100" s="36" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B100" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C100" s="49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D100" s="61" t="s">
-        <v>434</v>
+        <v>197</v>
       </c>
       <c r="E100" s="49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F100" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G100" s="52" t="s">
-        <v>435</v>
+        <v>88</v>
       </c>
       <c r="H100" s="49" t="s">
         <v>265</v>
@@ -7143,21 +7222,21 @@
       <c r="L100" s="46"/>
       <c r="N100" s="85"/>
       <c r="O100" s="59" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A101" s="36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B101" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C101" s="49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D101" s="61" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E101" s="49" t="s">
         <v>66</v>
@@ -7180,20 +7259,20 @@
         <v>249</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A102" s="36" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B102" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C102" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="D102" s="71" t="s">
-        <v>437</v>
-      </c>
-      <c r="E102" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="D102" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="E102" s="49" t="s">
         <v>66</v>
       </c>
       <c r="F102" s="49" t="s">
@@ -7214,20 +7293,20 @@
         <v>249</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A103" s="36" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B103" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C103" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="D103" s="61" t="s">
-        <v>438</v>
-      </c>
-      <c r="E103" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="D103" s="71" t="s">
+        <v>437</v>
+      </c>
+      <c r="E103" s="72" t="s">
         <v>66</v>
       </c>
       <c r="F103" s="49" t="s">
@@ -7248,18 +7327,18 @@
         <v>249</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A104" s="36" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B104" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C104" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D104" s="61" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E104" s="49" t="s">
         <v>66</v>
@@ -7282,9 +7361,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A105" s="36" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B105" s="60" t="s">
         <v>448</v>
@@ -7293,9 +7372,9 @@
         <v>187</v>
       </c>
       <c r="D105" s="61" t="s">
-        <v>440</v>
-      </c>
-      <c r="E105" s="80" t="s">
+        <v>439</v>
+      </c>
+      <c r="E105" s="49" t="s">
         <v>66</v>
       </c>
       <c r="F105" s="49" t="s">
@@ -7316,29 +7395,29 @@
         <v>249</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A106" s="36" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B106" s="60" t="s">
         <v>448</v>
       </c>
-      <c r="C106" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="D106" s="68" t="s">
-        <v>441</v>
-      </c>
-      <c r="E106" s="67" t="s">
+      <c r="C106" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D106" s="61" t="s">
+        <v>440</v>
+      </c>
+      <c r="E106" s="80" t="s">
         <v>66</v>
       </c>
       <c r="F106" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G106" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="H106" s="67" t="s">
+        <v>435</v>
+      </c>
+      <c r="H106" s="49" t="s">
         <v>265</v>
       </c>
       <c r="I106" s="36" t="s">
@@ -7350,127 +7429,128 @@
         <v>249</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A107" s="83" t="s">
-        <v>613</v>
-      </c>
-      <c r="B107" s="84" t="s">
+    <row r="107" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="36" t="s">
+        <v>553</v>
+      </c>
+      <c r="B107" s="60" t="s">
         <v>448</v>
       </c>
-      <c r="C107" s="80" t="s">
-        <v>609</v>
-      </c>
-      <c r="D107" s="81" t="s">
-        <v>610</v>
-      </c>
-      <c r="E107" s="92" t="s">
-        <v>611</v>
-      </c>
-      <c r="F107" s="80" t="s">
+      <c r="C107" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="D107" s="68" t="s">
+        <v>441</v>
+      </c>
+      <c r="E107" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="F107" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G107" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="G107" s="82" t="s">
-        <v>612</v>
-      </c>
-      <c r="H107" s="80" t="s">
+      <c r="H107" s="67" t="s">
         <v>265</v>
       </c>
-      <c r="I107" s="83" t="s">
-        <v>447</v>
+      <c r="I107" s="36" t="s">
+        <v>277</v>
       </c>
       <c r="L107" s="46"/>
       <c r="N107" s="85"/>
-    </row>
-    <row r="108" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A108" s="36" t="s">
+      <c r="O107" s="59" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A108" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="B108" s="84" t="s">
+        <v>448</v>
+      </c>
+      <c r="C108" s="80" t="s">
+        <v>609</v>
+      </c>
+      <c r="D108" s="81" t="s">
+        <v>610</v>
+      </c>
+      <c r="E108" s="92" t="s">
+        <v>611</v>
+      </c>
+      <c r="F108" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="G108" s="82" t="s">
+        <v>612</v>
+      </c>
+      <c r="H108" s="80" t="s">
+        <v>265</v>
+      </c>
+      <c r="I108" s="83" t="s">
+        <v>447</v>
+      </c>
+      <c r="L108" s="46"/>
+      <c r="N108" s="85"/>
+    </row>
+    <row r="109" spans="1:16" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A109" s="36" t="s">
         <v>554</v>
-      </c>
-      <c r="B108" s="60" t="s">
-        <v>448</v>
-      </c>
-      <c r="C108" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="D108" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="E108" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="F108" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G108" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="H108" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="I108" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="L108" s="46"/>
-      <c r="N108" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O108" s="59" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A109" s="36" t="s">
-        <v>555</v>
       </c>
       <c r="B109" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C109" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="D109" s="61" t="s">
-        <v>442</v>
+        <v>189</v>
+      </c>
+      <c r="D109" s="71" t="s">
+        <v>198</v>
       </c>
       <c r="E109" s="49" t="s">
-        <v>203</v>
+        <v>66</v>
       </c>
       <c r="F109" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G109" s="52" t="s">
-        <v>259</v>
+        <v>68</v>
       </c>
       <c r="H109" s="49" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I109" s="36" t="s">
         <v>277</v>
       </c>
       <c r="L109" s="46"/>
+      <c r="N109" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="O109" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A110" s="36" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B110" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C110" s="49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D110" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="E110" s="67" t="s">
-        <v>67</v>
+        <v>442</v>
+      </c>
+      <c r="E110" s="49" t="s">
+        <v>203</v>
       </c>
       <c r="F110" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G110" s="52" t="s">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="H110" s="49" t="s">
         <v>268</v>
@@ -7479,25 +7559,22 @@
         <v>277</v>
       </c>
       <c r="L110" s="46"/>
-      <c r="N110" s="2" t="s">
-        <v>632</v>
-      </c>
       <c r="O110" s="59" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A111" s="36" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B111" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C111" s="49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D111" s="61" t="s">
-        <v>443</v>
+        <v>199</v>
       </c>
       <c r="E111" s="67" t="s">
         <v>67</v>
@@ -7522,18 +7599,18 @@
         <v>235</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A112" s="36" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B112" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C112" s="49" t="s">
-        <v>323</v>
+        <v>192</v>
       </c>
       <c r="D112" s="61" t="s">
-        <v>367</v>
+        <v>443</v>
       </c>
       <c r="E112" s="67" t="s">
         <v>67</v>
@@ -7542,13 +7619,13 @@
         <v>232</v>
       </c>
       <c r="G112" s="52" t="s">
-        <v>368</v>
+        <v>206</v>
       </c>
       <c r="H112" s="49" t="s">
         <v>268</v>
       </c>
       <c r="I112" s="36" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L112" s="46"/>
       <c r="N112" s="2" t="s">
@@ -7558,18 +7635,18 @@
         <v>235</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" ht="102" x14ac:dyDescent="0.2">
       <c r="A113" s="36" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B113" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C113" s="49" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D113" s="61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E113" s="67" t="s">
         <v>67</v>
@@ -7578,7 +7655,7 @@
         <v>232</v>
       </c>
       <c r="G113" s="52" t="s">
-        <v>206</v>
+        <v>368</v>
       </c>
       <c r="H113" s="49" t="s">
         <v>268</v>
@@ -7594,18 +7671,18 @@
         <v>235</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="36" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B114" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C114" s="49" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D114" s="61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E114" s="67" t="s">
         <v>67</v>
@@ -7630,18 +7707,18 @@
         <v>235</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A115" s="36" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B115" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C115" s="49" t="s">
-        <v>63</v>
+        <v>325</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>64</v>
+        <v>365</v>
       </c>
       <c r="E115" s="67" t="s">
         <v>67</v>
@@ -7650,102 +7727,105 @@
         <v>232</v>
       </c>
       <c r="G115" s="52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H115" s="49" t="s">
         <v>268</v>
       </c>
       <c r="I115" s="36" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="L115" s="46"/>
-      <c r="N115" s="85"/>
-    </row>
-    <row r="116" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="N115" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="O115" s="59" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A116" s="36" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B116" s="60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C116" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="D116" s="63" t="s">
-        <v>379</v>
-      </c>
-      <c r="E116" s="49" t="s">
-        <v>380</v>
+        <v>63</v>
+      </c>
+      <c r="D116" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E116" s="67" t="s">
+        <v>67</v>
       </c>
       <c r="F116" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G116" s="52" t="s">
-        <v>355</v>
+        <v>207</v>
       </c>
       <c r="H116" s="49" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I116" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="J116" s="36"/>
-      <c r="K116" s="36"/>
-      <c r="N116" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="O116" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" ht="55.15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+      <c r="L116" s="46"/>
+      <c r="N116" s="85"/>
+    </row>
+    <row r="117" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A117" s="36" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B117" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C117" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="D117" s="61" t="s">
-        <v>200</v>
+        <v>378</v>
+      </c>
+      <c r="D117" s="63" t="s">
+        <v>379</v>
       </c>
       <c r="E117" s="49" t="s">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="F117" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="G117" s="82" t="s">
-        <v>43</v>
+      <c r="G117" s="52" t="s">
+        <v>355</v>
       </c>
       <c r="H117" s="49" t="s">
         <v>265</v>
       </c>
       <c r="I117" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="L117" s="46"/>
-      <c r="M117" s="102" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+      <c r="J117" s="36"/>
+      <c r="K117" s="36"/>
+      <c r="N117" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O117" s="59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="55.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="36" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B118" s="60" t="s">
         <v>450</v>
       </c>
       <c r="C118" s="49" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D118" s="61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E118" s="49" t="s">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="F118" s="49" t="s">
         <v>232</v>
@@ -7760,31 +7840,31 @@
         <v>277</v>
       </c>
       <c r="L118" s="46"/>
-      <c r="M118" s="102" t="s">
+      <c r="M118" s="85" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="153" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="36" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B119" s="60" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C119" s="49" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D119" s="61" t="s">
-        <v>295</v>
-      </c>
-      <c r="E119" s="67" t="s">
-        <v>205</v>
+        <v>201</v>
+      </c>
+      <c r="E119" s="49" t="s">
+        <v>204</v>
       </c>
       <c r="F119" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G119" s="82" t="s">
-        <v>643</v>
+        <v>43</v>
       </c>
       <c r="H119" s="49" t="s">
         <v>265</v>
@@ -7793,68 +7873,67 @@
         <v>277</v>
       </c>
       <c r="L119" s="46"/>
-      <c r="N119" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="O119" s="59" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="M119" s="85" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="153" x14ac:dyDescent="0.2">
       <c r="A120" s="36" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B120" s="60" t="s">
         <v>448</v>
       </c>
       <c r="C120" s="49" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D120" s="61" t="s">
-        <v>313</v>
-      </c>
-      <c r="E120" s="49" t="s">
-        <v>227</v>
+        <v>295</v>
+      </c>
+      <c r="E120" s="67" t="s">
+        <v>205</v>
       </c>
       <c r="F120" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="G120" s="52" t="s">
-        <v>314</v>
+      <c r="G120" s="82" t="s">
+        <v>643</v>
       </c>
       <c r="H120" s="49" t="s">
-        <v>230</v>
-      </c>
-      <c r="I120" s="83" t="s">
-        <v>286</v>
+        <v>265</v>
+      </c>
+      <c r="I120" s="36" t="s">
+        <v>277</v>
       </c>
       <c r="L120" s="46"/>
-      <c r="N120" s="85"/>
+      <c r="N120" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="O120" s="59" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A121" s="36" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B121" s="60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C121" s="49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D121" s="61" t="s">
-        <v>296</v>
-      </c>
-      <c r="E121" s="72" t="s">
-        <v>228</v>
+        <v>313</v>
+      </c>
+      <c r="E121" s="49" t="s">
+        <v>227</v>
       </c>
       <c r="F121" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G121" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H121" s="49" t="s">
         <v>230</v>
@@ -7863,34 +7942,32 @@
         <v>286</v>
       </c>
       <c r="L121" s="46"/>
-      <c r="N121" s="85" t="s">
-        <v>582</v>
-      </c>
+      <c r="N121" s="85"/>
       <c r="O121" s="59" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A122" s="36" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B122" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C122" s="49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D122" s="61" t="s">
-        <v>316</v>
-      </c>
-      <c r="E122" s="49" t="s">
-        <v>229</v>
+        <v>296</v>
+      </c>
+      <c r="E122" s="72" t="s">
+        <v>228</v>
       </c>
       <c r="F122" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G122" s="52" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H122" s="49" t="s">
         <v>230</v>
@@ -7899,31 +7976,34 @@
         <v>286</v>
       </c>
       <c r="L122" s="46"/>
+      <c r="N122" s="85" t="s">
+        <v>582</v>
+      </c>
       <c r="O122" s="59" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A123" s="36" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B123" s="60" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C123" s="49" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="D123" s="61" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="E123" s="49" t="s">
-        <v>357</v>
+        <v>229</v>
       </c>
       <c r="F123" s="49" t="s">
         <v>232</v>
       </c>
       <c r="G123" s="52" t="s">
-        <v>584</v>
+        <v>317</v>
       </c>
       <c r="H123" s="49" t="s">
         <v>230</v>
@@ -7938,115 +8018,123 @@
     </row>
     <row r="124" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A124" s="36" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B124" s="60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C124" s="49" t="s">
-        <v>648</v>
+        <v>281</v>
       </c>
       <c r="D124" s="61" t="s">
-        <v>614</v>
+        <v>297</v>
       </c>
       <c r="E124" s="49" t="s">
-        <v>640</v>
+        <v>357</v>
       </c>
       <c r="F124" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="G124" s="82" t="s">
-        <v>583</v>
-      </c>
-      <c r="H124" s="49"/>
+      <c r="G124" s="52" t="s">
+        <v>584</v>
+      </c>
+      <c r="H124" s="49" t="s">
+        <v>230</v>
+      </c>
       <c r="I124" s="83" t="s">
         <v>286</v>
       </c>
-      <c r="J124" s="88" t="s">
-        <v>447</v>
-      </c>
       <c r="L124" s="46"/>
       <c r="O124" s="59" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A125" s="36" t="s">
+        <v>570</v>
+      </c>
+      <c r="B125" s="60" t="s">
+        <v>450</v>
+      </c>
+      <c r="C125" s="49" t="s">
+        <v>648</v>
+      </c>
+      <c r="D125" s="61" t="s">
+        <v>614</v>
+      </c>
+      <c r="E125" s="49" t="s">
+        <v>640</v>
+      </c>
+      <c r="F125" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G125" s="82" t="s">
+        <v>583</v>
+      </c>
+      <c r="H125" s="49"/>
+      <c r="I125" s="83" t="s">
+        <v>286</v>
+      </c>
+      <c r="J125" s="88" t="s">
+        <v>447</v>
+      </c>
+      <c r="L125" s="46"/>
+      <c r="O125" s="59" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A125" s="103" t="s">
+    <row r="126" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A126" s="97" t="s">
         <v>615</v>
       </c>
-      <c r="B125" s="84" t="s">
+      <c r="B126" s="84" t="s">
         <v>450</v>
       </c>
-      <c r="C125" s="80" t="s">
+      <c r="C126" s="80" t="s">
         <v>585</v>
       </c>
-      <c r="D125" s="81" t="s">
+      <c r="D126" s="81" t="s">
         <v>586</v>
       </c>
-      <c r="E125" s="80" t="s">
+      <c r="E126" s="80" t="s">
         <v>587</v>
-      </c>
-      <c r="F125" s="80" t="s">
-        <v>232</v>
-      </c>
-      <c r="G125" s="82" t="s">
-        <v>588</v>
-      </c>
-      <c r="H125" s="80"/>
-      <c r="I125" s="83" t="s">
-        <v>447</v>
-      </c>
-      <c r="L125" s="46"/>
-    </row>
-    <row r="126" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A126" s="88" t="s">
-        <v>616</v>
-      </c>
-      <c r="B126" s="84" t="s">
-        <v>449</v>
-      </c>
-      <c r="C126" s="80" t="s">
-        <v>589</v>
-      </c>
-      <c r="D126" s="81" t="s">
-        <v>590</v>
-      </c>
-      <c r="E126" s="80" t="s">
-        <v>591</v>
       </c>
       <c r="F126" s="80" t="s">
         <v>232</v>
       </c>
       <c r="G126" s="82" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H126" s="80"/>
       <c r="I126" s="83" t="s">
         <v>447</v>
       </c>
       <c r="L126" s="46"/>
-    </row>
-    <row r="127" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="M126" s="85" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A127" s="88" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B127" s="84" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C127" s="80" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D127" s="81" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E127" s="80" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F127" s="80" t="s">
         <v>232</v>
       </c>
       <c r="G127" s="82" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H127" s="80"/>
       <c r="I127" s="83" t="s">
@@ -8056,25 +8144,25 @@
     </row>
     <row r="128" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A128" s="88" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B128" s="84" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C128" s="80" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D128" s="81" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E128" s="80" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F128" s="80" t="s">
         <v>232</v>
       </c>
       <c r="G128" s="82" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="H128" s="80"/>
       <c r="I128" s="83" t="s">
@@ -8082,22 +8170,39 @@
       </c>
       <c r="L128" s="46"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B129" s="39"/>
-      <c r="C129" s="40"/>
-      <c r="D129" s="41"/>
-      <c r="E129" s="40"/>
-      <c r="F129" s="40"/>
-      <c r="G129" s="52"/>
-      <c r="H129" s="40"/>
-      <c r="I129" s="36"/>
+    <row r="129" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A129" s="88" t="s">
+        <v>618</v>
+      </c>
+      <c r="B129" s="84" t="s">
+        <v>450</v>
+      </c>
+      <c r="C129" s="80" t="s">
+        <v>597</v>
+      </c>
+      <c r="D129" s="81" t="s">
+        <v>598</v>
+      </c>
+      <c r="E129" s="80" t="s">
+        <v>599</v>
+      </c>
+      <c r="F129" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="G129" s="82" t="s">
+        <v>600</v>
+      </c>
+      <c r="H129" s="80"/>
+      <c r="I129" s="83" t="s">
+        <v>447</v>
+      </c>
       <c r="L129" s="46"/>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B130" s="39"/>
-      <c r="C130" s="35"/>
-      <c r="D130" s="37"/>
-      <c r="E130" s="35"/>
+      <c r="C130" s="40"/>
+      <c r="D130" s="41"/>
+      <c r="E130" s="40"/>
       <c r="F130" s="40"/>
       <c r="G130" s="52"/>
       <c r="H130" s="40"/>
@@ -8117,8 +8222,8 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B132" s="39"/>
-      <c r="C132" s="40"/>
-      <c r="D132" s="41"/>
+      <c r="C132" s="35"/>
+      <c r="D132" s="37"/>
       <c r="E132" s="35"/>
       <c r="F132" s="40"/>
       <c r="G132" s="52"/>
@@ -8130,7 +8235,7 @@
       <c r="B133" s="39"/>
       <c r="C133" s="40"/>
       <c r="D133" s="41"/>
-      <c r="E133" s="40"/>
+      <c r="E133" s="35"/>
       <c r="F133" s="40"/>
       <c r="G133" s="52"/>
       <c r="H133" s="40"/>
@@ -8172,12 +8277,12 @@
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B137" s="39"/>
-      <c r="C137" s="35"/>
-      <c r="D137" s="37"/>
+      <c r="C137" s="40"/>
+      <c r="D137" s="41"/>
       <c r="E137" s="40"/>
       <c r="F137" s="40"/>
       <c r="G137" s="52"/>
-      <c r="H137" s="35"/>
+      <c r="H137" s="40"/>
       <c r="I137" s="36"/>
       <c r="L137" s="46"/>
     </row>
@@ -8205,12 +8310,12 @@
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B140" s="39"/>
-      <c r="C140" s="40"/>
-      <c r="D140" s="41"/>
+      <c r="C140" s="35"/>
+      <c r="D140" s="37"/>
       <c r="E140" s="40"/>
       <c r="F140" s="40"/>
       <c r="G140" s="52"/>
-      <c r="H140" s="40"/>
+      <c r="H140" s="35"/>
       <c r="I140" s="36"/>
       <c r="L140" s="46"/>
     </row>
@@ -8225,21 +8330,16 @@
       <c r="I141" s="36"/>
       <c r="L141" s="46"/>
     </row>
-    <row r="142" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="46"/>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B142" s="39"/>
       <c r="C142" s="40"/>
       <c r="D142" s="41"/>
       <c r="E142" s="40"/>
       <c r="F142" s="40"/>
       <c r="G142" s="52"/>
-      <c r="H142" s="35"/>
+      <c r="H142" s="40"/>
       <c r="I142" s="36"/>
-      <c r="J142" s="46"/>
-      <c r="K142" s="46"/>
       <c r="L142" s="46"/>
-      <c r="M142" s="101"/>
-      <c r="O142" s="59"/>
     </row>
     <row r="143" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="46"/>
@@ -8249,15 +8349,15 @@
       <c r="E143" s="40"/>
       <c r="F143" s="40"/>
       <c r="G143" s="52"/>
-      <c r="H143" s="40"/>
+      <c r="H143" s="35"/>
       <c r="I143" s="36"/>
       <c r="J143" s="46"/>
       <c r="K143" s="46"/>
       <c r="L143" s="46"/>
-      <c r="M143" s="101"/>
       <c r="O143" s="59"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="46"/>
       <c r="B144" s="39"/>
       <c r="C144" s="40"/>
       <c r="D144" s="41"/>
@@ -8266,7 +8366,10 @@
       <c r="G144" s="52"/>
       <c r="H144" s="40"/>
       <c r="I144" s="36"/>
+      <c r="J144" s="46"/>
+      <c r="K144" s="46"/>
       <c r="L144" s="46"/>
+      <c r="O144" s="59"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B145" s="39"/>
@@ -8281,12 +8384,12 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B146" s="39"/>
-      <c r="C146" s="35"/>
-      <c r="D146" s="37"/>
-      <c r="E146" s="35"/>
+      <c r="C146" s="40"/>
+      <c r="D146" s="41"/>
+      <c r="E146" s="40"/>
       <c r="F146" s="40"/>
       <c r="G146" s="52"/>
-      <c r="H146" s="35"/>
+      <c r="H146" s="40"/>
       <c r="I146" s="36"/>
       <c r="L146" s="46"/>
     </row>
@@ -8294,7 +8397,7 @@
       <c r="B147" s="39"/>
       <c r="C147" s="35"/>
       <c r="D147" s="37"/>
-      <c r="E147" s="40"/>
+      <c r="E147" s="35"/>
       <c r="F147" s="40"/>
       <c r="G147" s="52"/>
       <c r="H147" s="35"/>
@@ -8313,8 +8416,7 @@
       <c r="L148" s="46"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A149" s="36"/>
-      <c r="B149" s="40"/>
+      <c r="B149" s="39"/>
       <c r="C149" s="35"/>
       <c r="D149" s="37"/>
       <c r="E149" s="40"/>
@@ -8322,32 +8424,33 @@
       <c r="G149" s="52"/>
       <c r="H149" s="35"/>
       <c r="I149" s="36"/>
-      <c r="J149" s="36"/>
-      <c r="K149" s="36"/>
-    </row>
-    <row r="150" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="L149" s="46"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="36"/>
       <c r="B150" s="40"/>
       <c r="C150" s="35"/>
       <c r="D150" s="37"/>
       <c r="E150" s="40"/>
       <c r="F150" s="40"/>
-      <c r="G150" s="38"/>
+      <c r="G150" s="52"/>
       <c r="H150" s="35"/>
       <c r="I150" s="36"/>
       <c r="J150" s="36"/>
       <c r="K150" s="36"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B151" s="39"/>
+    <row r="151" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A151" s="36"/>
+      <c r="B151" s="40"/>
       <c r="C151" s="35"/>
       <c r="D151" s="37"/>
-      <c r="E151" s="35"/>
+      <c r="E151" s="40"/>
       <c r="F151" s="40"/>
-      <c r="G151" s="52"/>
+      <c r="G151" s="38"/>
       <c r="H151" s="35"/>
       <c r="I151" s="36"/>
-      <c r="L151" s="46"/>
+      <c r="J151" s="36"/>
+      <c r="K151" s="36"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B152" s="39"/>
@@ -8428,12 +8531,12 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B159" s="39"/>
-      <c r="C159" s="40"/>
-      <c r="D159" s="41"/>
-      <c r="E159" s="40"/>
+      <c r="C159" s="35"/>
+      <c r="D159" s="37"/>
+      <c r="E159" s="35"/>
       <c r="F159" s="40"/>
       <c r="G159" s="52"/>
-      <c r="H159" s="40"/>
+      <c r="H159" s="35"/>
       <c r="I159" s="36"/>
       <c r="L159" s="46"/>
     </row>
@@ -8461,53 +8564,53 @@
     </row>
     <row r="162" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B162" s="39"/>
-      <c r="C162" s="35"/>
-      <c r="D162" s="37"/>
+      <c r="C162" s="40"/>
+      <c r="D162" s="41"/>
       <c r="E162" s="40"/>
-      <c r="F162" s="35"/>
+      <c r="F162" s="40"/>
       <c r="G162" s="52"/>
-      <c r="H162" s="35"/>
+      <c r="H162" s="40"/>
       <c r="I162" s="36"/>
       <c r="L162" s="46"/>
     </row>
     <row r="163" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B163" s="39"/>
-      <c r="C163" s="40"/>
-      <c r="D163" s="41"/>
+      <c r="C163" s="35"/>
+      <c r="D163" s="37"/>
       <c r="E163" s="40"/>
       <c r="F163" s="35"/>
       <c r="G163" s="52"/>
-      <c r="H163" s="40"/>
+      <c r="H163" s="35"/>
       <c r="I163" s="36"/>
       <c r="L163" s="46"/>
     </row>
     <row r="164" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B164" s="39"/>
-      <c r="C164" s="35"/>
-      <c r="D164" s="37"/>
-      <c r="E164" s="35"/>
+      <c r="C164" s="40"/>
+      <c r="D164" s="41"/>
+      <c r="E164" s="40"/>
       <c r="F164" s="35"/>
       <c r="G164" s="52"/>
-      <c r="H164" s="35"/>
+      <c r="H164" s="40"/>
       <c r="I164" s="36"/>
       <c r="L164" s="46"/>
     </row>
     <row r="165" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B165" s="39"/>
-      <c r="C165" s="40"/>
-      <c r="D165" s="41"/>
-      <c r="E165" s="40"/>
+      <c r="C165" s="35"/>
+      <c r="D165" s="37"/>
+      <c r="E165" s="35"/>
       <c r="F165" s="35"/>
       <c r="G165" s="52"/>
-      <c r="H165" s="40"/>
+      <c r="H165" s="35"/>
       <c r="I165" s="36"/>
       <c r="L165" s="46"/>
     </row>
     <row r="166" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B166" s="39"/>
-      <c r="C166" s="47"/>
+      <c r="C166" s="40"/>
       <c r="D166" s="41"/>
-      <c r="E166" s="47"/>
+      <c r="E166" s="40"/>
       <c r="F166" s="35"/>
       <c r="G166" s="52"/>
       <c r="H166" s="40"/>
@@ -8516,9 +8619,9 @@
     </row>
     <row r="167" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B167" s="39"/>
-      <c r="C167" s="40"/>
+      <c r="C167" s="47"/>
       <c r="D167" s="41"/>
-      <c r="E167" s="40"/>
+      <c r="E167" s="47"/>
       <c r="F167" s="35"/>
       <c r="G167" s="52"/>
       <c r="H167" s="40"/>
@@ -8538,34 +8641,34 @@
     </row>
     <row r="169" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B169" s="39"/>
-      <c r="C169" s="35"/>
-      <c r="D169" s="37"/>
+      <c r="C169" s="40"/>
+      <c r="D169" s="41"/>
       <c r="E169" s="40"/>
       <c r="F169" s="35"/>
       <c r="G169" s="52"/>
-      <c r="H169" s="35"/>
+      <c r="H169" s="40"/>
       <c r="I169" s="36"/>
       <c r="L169" s="46"/>
     </row>
     <row r="170" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B170" s="39"/>
-      <c r="C170" s="40"/>
-      <c r="D170" s="41"/>
+      <c r="C170" s="35"/>
+      <c r="D170" s="37"/>
       <c r="E170" s="40"/>
       <c r="F170" s="35"/>
       <c r="G170" s="52"/>
-      <c r="H170" s="40"/>
+      <c r="H170" s="35"/>
       <c r="I170" s="36"/>
       <c r="L170" s="46"/>
     </row>
     <row r="171" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B171" s="39"/>
-      <c r="C171" s="35"/>
-      <c r="D171" s="37"/>
-      <c r="E171" s="35"/>
+      <c r="C171" s="40"/>
+      <c r="D171" s="41"/>
+      <c r="E171" s="40"/>
       <c r="F171" s="35"/>
       <c r="G171" s="52"/>
-      <c r="H171" s="35"/>
+      <c r="H171" s="40"/>
       <c r="I171" s="36"/>
       <c r="L171" s="46"/>
     </row>
@@ -8582,12 +8685,12 @@
     </row>
     <row r="173" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B173" s="39"/>
-      <c r="C173" s="40"/>
-      <c r="D173" s="41"/>
-      <c r="E173" s="40"/>
+      <c r="C173" s="35"/>
+      <c r="D173" s="37"/>
+      <c r="E173" s="35"/>
       <c r="F173" s="35"/>
       <c r="G173" s="52"/>
-      <c r="H173" s="40"/>
+      <c r="H173" s="35"/>
       <c r="I173" s="36"/>
       <c r="L173" s="46"/>
     </row>
@@ -8626,9 +8729,9 @@
     </row>
     <row r="177" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B177" s="39"/>
-      <c r="C177" s="35"/>
-      <c r="D177" s="37"/>
-      <c r="E177" s="35"/>
+      <c r="C177" s="40"/>
+      <c r="D177" s="41"/>
+      <c r="E177" s="40"/>
       <c r="F177" s="35"/>
       <c r="G177" s="52"/>
       <c r="H177" s="40"/>
@@ -8637,8 +8740,8 @@
     </row>
     <row r="178" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B178" s="39"/>
-      <c r="C178" s="40"/>
-      <c r="D178" s="41"/>
+      <c r="C178" s="35"/>
+      <c r="D178" s="37"/>
       <c r="E178" s="35"/>
       <c r="F178" s="35"/>
       <c r="G178" s="52"/>
@@ -8672,7 +8775,7 @@
       <c r="B181" s="39"/>
       <c r="C181" s="40"/>
       <c r="D181" s="41"/>
-      <c r="E181" s="40"/>
+      <c r="E181" s="35"/>
       <c r="F181" s="35"/>
       <c r="G181" s="52"/>
       <c r="H181" s="40"/>
@@ -8725,23 +8828,23 @@
     </row>
     <row r="186" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B186" s="39"/>
-      <c r="C186" s="35"/>
-      <c r="D186" s="37"/>
-      <c r="E186" s="35"/>
+      <c r="C186" s="40"/>
+      <c r="D186" s="41"/>
+      <c r="E186" s="40"/>
       <c r="F186" s="35"/>
       <c r="G186" s="52"/>
-      <c r="H186" s="35"/>
+      <c r="H186" s="40"/>
       <c r="I186" s="36"/>
       <c r="L186" s="46"/>
     </row>
     <row r="187" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B187" s="39"/>
-      <c r="C187" s="40"/>
-      <c r="D187" s="41"/>
-      <c r="E187" s="40"/>
+      <c r="C187" s="35"/>
+      <c r="D187" s="37"/>
+      <c r="E187" s="35"/>
       <c r="F187" s="35"/>
       <c r="G187" s="52"/>
-      <c r="H187" s="40"/>
+      <c r="H187" s="35"/>
       <c r="I187" s="36"/>
       <c r="L187" s="46"/>
     </row>
@@ -8758,23 +8861,23 @@
     </row>
     <row r="189" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B189" s="39"/>
-      <c r="C189" s="35"/>
-      <c r="D189" s="37"/>
-      <c r="E189" s="35"/>
+      <c r="C189" s="40"/>
+      <c r="D189" s="41"/>
+      <c r="E189" s="40"/>
       <c r="F189" s="35"/>
       <c r="G189" s="52"/>
-      <c r="H189" s="35"/>
+      <c r="H189" s="40"/>
       <c r="I189" s="36"/>
       <c r="L189" s="46"/>
     </row>
     <row r="190" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B190" s="39"/>
-      <c r="C190" s="40"/>
-      <c r="D190" s="41"/>
-      <c r="E190" s="40"/>
+      <c r="C190" s="35"/>
+      <c r="D190" s="37"/>
+      <c r="E190" s="35"/>
       <c r="F190" s="35"/>
       <c r="G190" s="52"/>
-      <c r="H190" s="40"/>
+      <c r="H190" s="35"/>
       <c r="I190" s="36"/>
       <c r="L190" s="46"/>
     </row>
@@ -8967,23 +9070,23 @@
     </row>
     <row r="208" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B208" s="39"/>
-      <c r="C208" s="35"/>
-      <c r="D208" s="37"/>
-      <c r="E208" s="35"/>
+      <c r="C208" s="40"/>
+      <c r="D208" s="41"/>
+      <c r="E208" s="40"/>
       <c r="F208" s="35"/>
       <c r="G208" s="52"/>
-      <c r="H208" s="35"/>
+      <c r="H208" s="40"/>
       <c r="I208" s="36"/>
       <c r="L208" s="46"/>
     </row>
     <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="39"/>
-      <c r="C209" s="40"/>
-      <c r="D209" s="41"/>
-      <c r="E209" s="40"/>
+      <c r="C209" s="35"/>
+      <c r="D209" s="37"/>
+      <c r="E209" s="35"/>
       <c r="F209" s="35"/>
       <c r="G209" s="52"/>
-      <c r="H209" s="40"/>
+      <c r="H209" s="35"/>
       <c r="I209" s="36"/>
       <c r="L209" s="46"/>
     </row>
@@ -9088,45 +9191,45 @@
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B219" s="39"/>
-      <c r="C219" s="35"/>
-      <c r="D219" s="37"/>
-      <c r="E219" s="35"/>
+      <c r="C219" s="40"/>
+      <c r="D219" s="41"/>
+      <c r="E219" s="40"/>
       <c r="F219" s="35"/>
       <c r="G219" s="52"/>
-      <c r="H219" s="35"/>
+      <c r="H219" s="40"/>
       <c r="I219" s="36"/>
       <c r="L219" s="46"/>
     </row>
     <row r="220" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B220" s="39"/>
-      <c r="C220" s="40"/>
-      <c r="D220" s="41"/>
-      <c r="E220" s="40"/>
+      <c r="C220" s="35"/>
+      <c r="D220" s="37"/>
+      <c r="E220" s="35"/>
       <c r="F220" s="35"/>
       <c r="G220" s="52"/>
-      <c r="H220" s="40"/>
+      <c r="H220" s="35"/>
       <c r="I220" s="36"/>
       <c r="L220" s="46"/>
     </row>
     <row r="221" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B221" s="39"/>
-      <c r="C221" s="35"/>
-      <c r="D221" s="37"/>
-      <c r="E221" s="35"/>
+      <c r="C221" s="40"/>
+      <c r="D221" s="41"/>
+      <c r="E221" s="40"/>
       <c r="F221" s="35"/>
       <c r="G221" s="52"/>
-      <c r="H221" s="35"/>
+      <c r="H221" s="40"/>
       <c r="I221" s="36"/>
       <c r="L221" s="46"/>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B222" s="39"/>
-      <c r="C222" s="40"/>
-      <c r="D222" s="41"/>
-      <c r="E222" s="40"/>
+      <c r="C222" s="35"/>
+      <c r="D222" s="37"/>
+      <c r="E222" s="35"/>
       <c r="F222" s="35"/>
       <c r="G222" s="52"/>
-      <c r="H222" s="40"/>
+      <c r="H222" s="35"/>
       <c r="I222" s="36"/>
       <c r="L222" s="46"/>
     </row>
@@ -9209,23 +9312,23 @@
     </row>
     <row r="230" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B230" s="39"/>
-      <c r="C230" s="35"/>
-      <c r="D230" s="37"/>
-      <c r="E230" s="35"/>
+      <c r="C230" s="40"/>
+      <c r="D230" s="41"/>
+      <c r="E230" s="40"/>
       <c r="F230" s="35"/>
       <c r="G230" s="52"/>
-      <c r="H230" s="35"/>
+      <c r="H230" s="40"/>
       <c r="I230" s="36"/>
       <c r="L230" s="46"/>
     </row>
     <row r="231" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B231" s="39"/>
-      <c r="C231" s="40"/>
-      <c r="D231" s="41"/>
-      <c r="E231" s="40"/>
+      <c r="C231" s="35"/>
+      <c r="D231" s="37"/>
+      <c r="E231" s="35"/>
       <c r="F231" s="35"/>
       <c r="G231" s="52"/>
-      <c r="H231" s="40"/>
+      <c r="H231" s="35"/>
       <c r="I231" s="36"/>
       <c r="L231" s="46"/>
     </row>
@@ -9275,23 +9378,23 @@
     </row>
     <row r="236" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B236" s="39"/>
-      <c r="C236" s="35"/>
-      <c r="D236" s="37"/>
+      <c r="C236" s="40"/>
+      <c r="D236" s="41"/>
       <c r="E236" s="40"/>
       <c r="F236" s="35"/>
       <c r="G236" s="52"/>
-      <c r="H236" s="35"/>
+      <c r="H236" s="40"/>
       <c r="I236" s="36"/>
       <c r="L236" s="46"/>
     </row>
     <row r="237" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B237" s="39"/>
-      <c r="C237" s="40"/>
-      <c r="D237" s="41"/>
+      <c r="C237" s="35"/>
+      <c r="D237" s="37"/>
       <c r="E237" s="40"/>
       <c r="F237" s="35"/>
       <c r="G237" s="52"/>
-      <c r="H237" s="40"/>
+      <c r="H237" s="35"/>
       <c r="I237" s="36"/>
       <c r="L237" s="46"/>
     </row>
@@ -9319,34 +9422,34 @@
     </row>
     <row r="240" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B240" s="39"/>
-      <c r="C240" s="35"/>
-      <c r="D240" s="37"/>
+      <c r="C240" s="40"/>
+      <c r="D240" s="41"/>
       <c r="E240" s="40"/>
       <c r="F240" s="35"/>
       <c r="G240" s="52"/>
-      <c r="H240" s="35"/>
+      <c r="H240" s="40"/>
       <c r="I240" s="36"/>
       <c r="L240" s="46"/>
     </row>
     <row r="241" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B241" s="39"/>
-      <c r="C241" s="40"/>
-      <c r="D241" s="41"/>
+      <c r="C241" s="35"/>
+      <c r="D241" s="37"/>
       <c r="E241" s="40"/>
       <c r="F241" s="35"/>
       <c r="G241" s="52"/>
-      <c r="H241" s="40"/>
+      <c r="H241" s="35"/>
       <c r="I241" s="36"/>
       <c r="L241" s="46"/>
     </row>
     <row r="242" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B242" s="39"/>
-      <c r="C242" s="35"/>
-      <c r="D242" s="37"/>
-      <c r="E242" s="35"/>
+      <c r="C242" s="40"/>
+      <c r="D242" s="41"/>
+      <c r="E242" s="40"/>
       <c r="F242" s="35"/>
       <c r="G242" s="52"/>
-      <c r="H242" s="35"/>
+      <c r="H242" s="40"/>
       <c r="I242" s="36"/>
       <c r="L242" s="46"/>
     </row>
@@ -9363,9 +9466,9 @@
     </row>
     <row r="244" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B244" s="39"/>
-      <c r="C244" s="40"/>
-      <c r="D244" s="41"/>
-      <c r="E244" s="40"/>
+      <c r="C244" s="35"/>
+      <c r="D244" s="37"/>
+      <c r="E244" s="35"/>
       <c r="F244" s="35"/>
       <c r="G244" s="52"/>
       <c r="H244" s="35"/>
@@ -9401,7 +9504,7 @@
       <c r="E247" s="40"/>
       <c r="F247" s="35"/>
       <c r="G247" s="52"/>
-      <c r="H247" s="40"/>
+      <c r="H247" s="35"/>
       <c r="I247" s="36"/>
       <c r="L247" s="46"/>
     </row>
@@ -9440,12 +9543,12 @@
     </row>
     <row r="251" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B251" s="39"/>
-      <c r="C251" s="35"/>
-      <c r="D251" s="37"/>
-      <c r="E251" s="35"/>
+      <c r="C251" s="40"/>
+      <c r="D251" s="41"/>
+      <c r="E251" s="40"/>
       <c r="F251" s="35"/>
       <c r="G251" s="52"/>
-      <c r="H251" s="35"/>
+      <c r="H251" s="40"/>
       <c r="I251" s="36"/>
       <c r="L251" s="46"/>
     </row>
@@ -9484,12 +9587,12 @@
     </row>
     <row r="255" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B255" s="39"/>
-      <c r="C255" s="40"/>
+      <c r="C255" s="35"/>
       <c r="D255" s="37"/>
-      <c r="E255" s="40"/>
+      <c r="E255" s="35"/>
       <c r="F255" s="35"/>
       <c r="G255" s="52"/>
-      <c r="H255" s="40"/>
+      <c r="H255" s="35"/>
       <c r="I255" s="36"/>
       <c r="L255" s="46"/>
     </row>
@@ -9507,7 +9610,7 @@
     <row r="257" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B257" s="39"/>
       <c r="C257" s="40"/>
-      <c r="D257" s="41"/>
+      <c r="D257" s="37"/>
       <c r="E257" s="40"/>
       <c r="F257" s="35"/>
       <c r="G257" s="52"/>
@@ -9572,18 +9675,18 @@
     </row>
     <row r="263" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B263" s="39"/>
-      <c r="C263" s="35"/>
-      <c r="D263" s="37"/>
+      <c r="C263" s="40"/>
+      <c r="D263" s="41"/>
       <c r="E263" s="40"/>
       <c r="F263" s="35"/>
       <c r="G263" s="52"/>
-      <c r="H263" s="35"/>
+      <c r="H263" s="40"/>
       <c r="I263" s="36"/>
       <c r="L263" s="46"/>
     </row>
     <row r="264" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B264" s="39"/>
-      <c r="C264" s="40"/>
+      <c r="C264" s="35"/>
       <c r="D264" s="37"/>
       <c r="E264" s="40"/>
       <c r="F264" s="35"/>
@@ -9599,14 +9702,14 @@
       <c r="E265" s="40"/>
       <c r="F265" s="35"/>
       <c r="G265" s="52"/>
-      <c r="H265" s="40"/>
+      <c r="H265" s="35"/>
       <c r="I265" s="36"/>
       <c r="L265" s="46"/>
     </row>
     <row r="266" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B266" s="39"/>
       <c r="C266" s="40"/>
-      <c r="D266" s="41"/>
+      <c r="D266" s="37"/>
       <c r="E266" s="40"/>
       <c r="F266" s="35"/>
       <c r="G266" s="52"/>
@@ -9630,7 +9733,7 @@
       <c r="C268" s="40"/>
       <c r="D268" s="41"/>
       <c r="E268" s="40"/>
-      <c r="F268" s="40"/>
+      <c r="F268" s="35"/>
       <c r="G268" s="52"/>
       <c r="H268" s="40"/>
       <c r="I268" s="36"/>
@@ -9641,7 +9744,7 @@
       <c r="C269" s="40"/>
       <c r="D269" s="41"/>
       <c r="E269" s="40"/>
-      <c r="F269" s="35"/>
+      <c r="F269" s="40"/>
       <c r="G269" s="52"/>
       <c r="H269" s="40"/>
       <c r="I269" s="36"/>
@@ -9704,8 +9807,8 @@
     </row>
     <row r="275" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B275" s="39"/>
-      <c r="C275" s="35"/>
-      <c r="D275" s="37"/>
+      <c r="C275" s="40"/>
+      <c r="D275" s="41"/>
       <c r="E275" s="40"/>
       <c r="F275" s="35"/>
       <c r="G275" s="52"/>
@@ -9717,7 +9820,7 @@
       <c r="B276" s="39"/>
       <c r="C276" s="35"/>
       <c r="D276" s="37"/>
-      <c r="E276" s="35"/>
+      <c r="E276" s="40"/>
       <c r="F276" s="35"/>
       <c r="G276" s="52"/>
       <c r="H276" s="40"/>
@@ -9726,9 +9829,9 @@
     </row>
     <row r="277" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B277" s="39"/>
-      <c r="C277" s="40"/>
+      <c r="C277" s="35"/>
       <c r="D277" s="37"/>
-      <c r="E277" s="40"/>
+      <c r="E277" s="35"/>
       <c r="F277" s="35"/>
       <c r="G277" s="52"/>
       <c r="H277" s="40"/>
@@ -9749,7 +9852,7 @@
     <row r="279" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B279" s="39"/>
       <c r="C279" s="40"/>
-      <c r="D279" s="41"/>
+      <c r="D279" s="37"/>
       <c r="E279" s="40"/>
       <c r="F279" s="35"/>
       <c r="G279" s="52"/>
@@ -9781,8 +9884,8 @@
     </row>
     <row r="282" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B282" s="39"/>
-      <c r="C282" s="35"/>
-      <c r="D282" s="37"/>
+      <c r="C282" s="40"/>
+      <c r="D282" s="41"/>
       <c r="E282" s="40"/>
       <c r="F282" s="35"/>
       <c r="G282" s="52"/>
@@ -9792,8 +9895,8 @@
     </row>
     <row r="283" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B283" s="39"/>
-      <c r="C283" s="40"/>
-      <c r="D283" s="41"/>
+      <c r="C283" s="35"/>
+      <c r="D283" s="37"/>
       <c r="E283" s="40"/>
       <c r="F283" s="35"/>
       <c r="G283" s="52"/>
@@ -9880,8 +9983,8 @@
     </row>
     <row r="291" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B291" s="39"/>
-      <c r="C291" s="35"/>
-      <c r="D291" s="37"/>
+      <c r="C291" s="40"/>
+      <c r="D291" s="41"/>
       <c r="E291" s="40"/>
       <c r="F291" s="35"/>
       <c r="G291" s="52"/>
@@ -9891,7 +9994,7 @@
     </row>
     <row r="292" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B292" s="39"/>
-      <c r="C292" s="40"/>
+      <c r="C292" s="35"/>
       <c r="D292" s="37"/>
       <c r="E292" s="40"/>
       <c r="F292" s="35"/>
@@ -9925,7 +10028,7 @@
     <row r="295" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B295" s="39"/>
       <c r="C295" s="40"/>
-      <c r="D295" s="41"/>
+      <c r="D295" s="37"/>
       <c r="E295" s="40"/>
       <c r="F295" s="35"/>
       <c r="G295" s="52"/>
@@ -9936,7 +10039,7 @@
     <row r="296" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B296" s="39"/>
       <c r="C296" s="40"/>
-      <c r="D296" s="37"/>
+      <c r="D296" s="41"/>
       <c r="E296" s="40"/>
       <c r="F296" s="35"/>
       <c r="G296" s="52"/>
@@ -9947,7 +10050,7 @@
     <row r="297" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B297" s="39"/>
       <c r="C297" s="40"/>
-      <c r="D297" s="41"/>
+      <c r="D297" s="37"/>
       <c r="E297" s="40"/>
       <c r="F297" s="35"/>
       <c r="G297" s="52"/>
@@ -9980,7 +10083,7 @@
     <row r="300" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B300" s="39"/>
       <c r="C300" s="40"/>
-      <c r="D300" s="37"/>
+      <c r="D300" s="41"/>
       <c r="E300" s="40"/>
       <c r="F300" s="35"/>
       <c r="G300" s="52"/>
@@ -10001,7 +10104,7 @@
     </row>
     <row r="302" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B302" s="39"/>
-      <c r="C302" s="35"/>
+      <c r="C302" s="40"/>
       <c r="D302" s="37"/>
       <c r="E302" s="40"/>
       <c r="F302" s="35"/>
@@ -10012,8 +10115,8 @@
     </row>
     <row r="303" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B303" s="39"/>
-      <c r="C303" s="40"/>
-      <c r="D303" s="41"/>
+      <c r="C303" s="35"/>
+      <c r="D303" s="37"/>
       <c r="E303" s="40"/>
       <c r="F303" s="35"/>
       <c r="G303" s="52"/>
@@ -10024,7 +10127,7 @@
     <row r="304" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B304" s="39"/>
       <c r="C304" s="40"/>
-      <c r="D304" s="37"/>
+      <c r="D304" s="41"/>
       <c r="E304" s="40"/>
       <c r="F304" s="35"/>
       <c r="G304" s="52"/>
@@ -10035,7 +10138,7 @@
     <row r="305" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B305" s="39"/>
       <c r="C305" s="40"/>
-      <c r="D305" s="41"/>
+      <c r="D305" s="37"/>
       <c r="E305" s="40"/>
       <c r="F305" s="35"/>
       <c r="G305" s="52"/>
@@ -10045,9 +10148,9 @@
     </row>
     <row r="306" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B306" s="39"/>
-      <c r="C306" s="35"/>
-      <c r="D306" s="37"/>
-      <c r="E306" s="35"/>
+      <c r="C306" s="40"/>
+      <c r="D306" s="41"/>
+      <c r="E306" s="40"/>
       <c r="F306" s="35"/>
       <c r="G306" s="52"/>
       <c r="H306" s="40"/>
@@ -10078,9 +10181,9 @@
     </row>
     <row r="309" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B309" s="39"/>
-      <c r="C309" s="40"/>
+      <c r="C309" s="35"/>
       <c r="D309" s="37"/>
-      <c r="E309" s="40"/>
+      <c r="E309" s="35"/>
       <c r="F309" s="35"/>
       <c r="G309" s="52"/>
       <c r="H309" s="40"/>
@@ -10090,7 +10193,7 @@
     <row r="310" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B310" s="39"/>
       <c r="C310" s="40"/>
-      <c r="D310" s="41"/>
+      <c r="D310" s="37"/>
       <c r="E310" s="40"/>
       <c r="F310" s="35"/>
       <c r="G310" s="52"/>
@@ -10133,9 +10236,9 @@
     </row>
     <row r="314" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B314" s="39"/>
-      <c r="C314" s="35"/>
-      <c r="D314" s="37"/>
-      <c r="E314" s="35"/>
+      <c r="C314" s="40"/>
+      <c r="D314" s="41"/>
+      <c r="E314" s="40"/>
       <c r="F314" s="35"/>
       <c r="G314" s="52"/>
       <c r="H314" s="40"/>
@@ -10155,9 +10258,9 @@
     </row>
     <row r="316" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B316" s="39"/>
-      <c r="C316" s="40"/>
-      <c r="D316" s="41"/>
-      <c r="E316" s="40"/>
+      <c r="C316" s="35"/>
+      <c r="D316" s="37"/>
+      <c r="E316" s="35"/>
       <c r="F316" s="35"/>
       <c r="G316" s="52"/>
       <c r="H316" s="40"/>
@@ -10222,7 +10325,7 @@
     <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B322" s="39"/>
       <c r="C322" s="40"/>
-      <c r="D322" s="37"/>
+      <c r="D322" s="41"/>
       <c r="E322" s="40"/>
       <c r="F322" s="35"/>
       <c r="G322" s="52"/>
@@ -10233,7 +10336,7 @@
     <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B323" s="39"/>
       <c r="C323" s="40"/>
-      <c r="D323" s="41"/>
+      <c r="D323" s="37"/>
       <c r="E323" s="40"/>
       <c r="F323" s="35"/>
       <c r="G323" s="52"/>
@@ -10241,30 +10344,30 @@
       <c r="I323" s="36"/>
       <c r="L323" s="46"/>
     </row>
-    <row r="324" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A324" s="36"/>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B324" s="39"/>
-      <c r="C324" s="43"/>
-      <c r="D324" s="44"/>
-      <c r="E324" s="43"/>
-      <c r="F324" s="40"/>
+      <c r="C324" s="40"/>
+      <c r="D324" s="41"/>
+      <c r="E324" s="40"/>
+      <c r="F324" s="35"/>
       <c r="G324" s="52"/>
-      <c r="H324" s="45"/>
+      <c r="H324" s="40"/>
       <c r="I324" s="36"/>
-      <c r="J324" s="36"/>
-      <c r="K324" s="36"/>
-      <c r="N324" s="42"/>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L324" s="46"/>
+    </row>
+    <row r="325" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+      <c r="A325" s="36"/>
       <c r="B325" s="39"/>
-      <c r="C325" s="40"/>
-      <c r="D325" s="41"/>
-      <c r="E325" s="40"/>
-      <c r="F325" s="35"/>
+      <c r="C325" s="43"/>
+      <c r="D325" s="44"/>
+      <c r="E325" s="43"/>
+      <c r="F325" s="40"/>
       <c r="G325" s="52"/>
-      <c r="H325" s="40"/>
+      <c r="H325" s="45"/>
       <c r="I325" s="36"/>
-      <c r="L325" s="46"/>
+      <c r="J325" s="36"/>
+      <c r="K325" s="36"/>
+      <c r="N325" s="42"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B326" s="39"/>
@@ -10301,23 +10404,23 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B329" s="39"/>
-      <c r="C329" s="35"/>
-      <c r="D329" s="37"/>
+      <c r="C329" s="40"/>
+      <c r="D329" s="41"/>
       <c r="E329" s="40"/>
       <c r="F329" s="35"/>
       <c r="G329" s="52"/>
-      <c r="H329" s="35"/>
+      <c r="H329" s="40"/>
       <c r="I329" s="36"/>
       <c r="L329" s="46"/>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B330" s="39"/>
-      <c r="C330" s="40"/>
-      <c r="D330" s="41"/>
+      <c r="C330" s="35"/>
+      <c r="D330" s="37"/>
       <c r="E330" s="40"/>
       <c r="F330" s="35"/>
       <c r="G330" s="52"/>
-      <c r="H330" s="40"/>
+      <c r="H330" s="35"/>
       <c r="I330" s="36"/>
       <c r="L330" s="46"/>
     </row>
@@ -10548,7 +10651,7 @@
       <c r="E351" s="40"/>
       <c r="F351" s="35"/>
       <c r="G351" s="52"/>
-      <c r="H351" s="35"/>
+      <c r="H351" s="40"/>
       <c r="I351" s="36"/>
       <c r="L351" s="46"/>
     </row>
@@ -10559,13 +10662,13 @@
       <c r="E352" s="40"/>
       <c r="F352" s="35"/>
       <c r="G352" s="52"/>
-      <c r="H352" s="40"/>
+      <c r="H352" s="35"/>
       <c r="I352" s="36"/>
       <c r="L352" s="46"/>
     </row>
     <row r="353" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B353" s="39"/>
-      <c r="C353" s="39"/>
+      <c r="C353" s="40"/>
       <c r="D353" s="41"/>
       <c r="E353" s="40"/>
       <c r="F353" s="35"/>
@@ -10576,7 +10679,7 @@
     </row>
     <row r="354" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B354" s="39"/>
-      <c r="C354" s="40"/>
+      <c r="C354" s="39"/>
       <c r="D354" s="41"/>
       <c r="E354" s="40"/>
       <c r="F354" s="35"/>
@@ -10642,20 +10745,20 @@
     </row>
     <row r="360" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B360" s="39"/>
-      <c r="C360" s="35"/>
-      <c r="D360" s="37"/>
+      <c r="C360" s="40"/>
+      <c r="D360" s="41"/>
       <c r="E360" s="40"/>
       <c r="F360" s="35"/>
       <c r="G360" s="52"/>
-      <c r="H360" s="35"/>
+      <c r="H360" s="40"/>
       <c r="I360" s="36"/>
       <c r="L360" s="46"/>
     </row>
     <row r="361" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B361" s="39"/>
-      <c r="C361" s="40"/>
+      <c r="C361" s="35"/>
       <c r="D361" s="37"/>
-      <c r="E361" s="35"/>
+      <c r="E361" s="40"/>
       <c r="F361" s="35"/>
       <c r="G361" s="52"/>
       <c r="H361" s="35"/>
@@ -10665,11 +10768,11 @@
     <row r="362" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B362" s="39"/>
       <c r="C362" s="40"/>
-      <c r="D362" s="41"/>
-      <c r="E362" s="40"/>
+      <c r="D362" s="37"/>
+      <c r="E362" s="35"/>
       <c r="F362" s="35"/>
       <c r="G362" s="52"/>
-      <c r="H362" s="40"/>
+      <c r="H362" s="35"/>
       <c r="I362" s="36"/>
       <c r="L362" s="46"/>
     </row>
@@ -10753,9 +10856,9 @@
     <row r="370" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B370" s="39"/>
       <c r="C370" s="40"/>
-      <c r="D370" s="40"/>
+      <c r="D370" s="41"/>
       <c r="E370" s="40"/>
-      <c r="F370" s="40"/>
+      <c r="F370" s="35"/>
       <c r="G370" s="52"/>
       <c r="H370" s="40"/>
       <c r="I370" s="36"/>
@@ -10829,23 +10932,23 @@
     </row>
     <row r="377" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B377" s="39"/>
-      <c r="C377" s="35"/>
-      <c r="D377" s="35"/>
-      <c r="E377" s="35"/>
-      <c r="F377" s="35"/>
+      <c r="C377" s="40"/>
+      <c r="D377" s="40"/>
+      <c r="E377" s="40"/>
+      <c r="F377" s="40"/>
       <c r="G377" s="52"/>
-      <c r="H377" s="35"/>
+      <c r="H377" s="40"/>
       <c r="I377" s="36"/>
       <c r="L377" s="46"/>
     </row>
     <row r="378" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B378" s="39"/>
-      <c r="C378" s="40"/>
-      <c r="D378" s="40"/>
-      <c r="E378" s="40"/>
-      <c r="F378" s="40"/>
+      <c r="C378" s="35"/>
+      <c r="D378" s="35"/>
+      <c r="E378" s="35"/>
+      <c r="F378" s="35"/>
       <c r="G378" s="52"/>
-      <c r="H378" s="40"/>
+      <c r="H378" s="35"/>
       <c r="I378" s="36"/>
       <c r="L378" s="46"/>
     </row>
@@ -10972,23 +11075,23 @@
     </row>
     <row r="390" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B390" s="39"/>
-      <c r="C390" s="35"/>
-      <c r="D390" s="35"/>
-      <c r="E390" s="35"/>
-      <c r="F390" s="35"/>
+      <c r="C390" s="40"/>
+      <c r="D390" s="40"/>
+      <c r="E390" s="40"/>
+      <c r="F390" s="40"/>
       <c r="G390" s="52"/>
-      <c r="H390" s="35"/>
+      <c r="H390" s="40"/>
       <c r="I390" s="36"/>
       <c r="L390" s="46"/>
     </row>
     <row r="391" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B391" s="39"/>
-      <c r="C391" s="40"/>
-      <c r="D391" s="40"/>
-      <c r="E391" s="40"/>
-      <c r="F391" s="40"/>
+      <c r="C391" s="35"/>
+      <c r="D391" s="35"/>
+      <c r="E391" s="35"/>
+      <c r="F391" s="35"/>
       <c r="G391" s="52"/>
-      <c r="H391" s="40"/>
+      <c r="H391" s="35"/>
       <c r="I391" s="36"/>
       <c r="L391" s="46"/>
     </row>
@@ -11007,8 +11110,8 @@
       <c r="B393" s="39"/>
       <c r="C393" s="40"/>
       <c r="D393" s="40"/>
-      <c r="E393" s="48"/>
-      <c r="F393" s="48"/>
+      <c r="E393" s="40"/>
+      <c r="F393" s="40"/>
       <c r="G393" s="52"/>
       <c r="H393" s="40"/>
       <c r="I393" s="36"/>
@@ -11016,30 +11119,30 @@
     </row>
     <row r="394" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B394" s="39"/>
-      <c r="C394" s="35"/>
-      <c r="D394" s="35"/>
-      <c r="E394" s="35"/>
-      <c r="F394" s="35"/>
+      <c r="C394" s="40"/>
+      <c r="D394" s="40"/>
+      <c r="E394" s="48"/>
+      <c r="F394" s="48"/>
       <c r="G394" s="52"/>
-      <c r="H394" s="35"/>
+      <c r="H394" s="40"/>
       <c r="I394" s="36"/>
       <c r="L394" s="46"/>
     </row>
     <row r="395" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B395" s="39"/>
-      <c r="C395" s="40"/>
-      <c r="D395" s="40"/>
-      <c r="E395" s="40"/>
-      <c r="F395" s="40"/>
+      <c r="C395" s="35"/>
+      <c r="D395" s="35"/>
+      <c r="E395" s="35"/>
+      <c r="F395" s="35"/>
       <c r="G395" s="52"/>
-      <c r="H395" s="40"/>
+      <c r="H395" s="35"/>
       <c r="I395" s="36"/>
       <c r="L395" s="46"/>
     </row>
     <row r="396" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B396" s="39"/>
       <c r="C396" s="40"/>
-      <c r="D396" s="49"/>
+      <c r="D396" s="40"/>
       <c r="E396" s="40"/>
       <c r="F396" s="40"/>
       <c r="G396" s="52"/>
@@ -11049,10 +11152,10 @@
     </row>
     <row r="397" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B397" s="39"/>
-      <c r="C397" s="48"/>
-      <c r="D397" s="40"/>
-      <c r="E397" s="48"/>
-      <c r="F397" s="48"/>
+      <c r="C397" s="40"/>
+      <c r="D397" s="49"/>
+      <c r="E397" s="40"/>
+      <c r="F397" s="40"/>
       <c r="G397" s="52"/>
       <c r="H397" s="40"/>
       <c r="I397" s="36"/>
@@ -11060,10 +11163,10 @@
     </row>
     <row r="398" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B398" s="39"/>
-      <c r="C398" s="40"/>
+      <c r="C398" s="48"/>
       <c r="D398" s="40"/>
-      <c r="E398" s="40"/>
-      <c r="F398" s="40"/>
+      <c r="E398" s="48"/>
+      <c r="F398" s="48"/>
       <c r="G398" s="52"/>
       <c r="H398" s="40"/>
       <c r="I398" s="36"/>
@@ -11148,23 +11251,23 @@
     </row>
     <row r="406" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B406" s="39"/>
-      <c r="C406" s="48"/>
+      <c r="C406" s="40"/>
       <c r="D406" s="40"/>
       <c r="E406" s="40"/>
       <c r="F406" s="40"/>
       <c r="G406" s="52"/>
-      <c r="H406" s="50"/>
+      <c r="H406" s="40"/>
       <c r="I406" s="36"/>
       <c r="L406" s="46"/>
     </row>
     <row r="407" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B407" s="39"/>
-      <c r="C407" s="40"/>
+      <c r="C407" s="48"/>
       <c r="D407" s="40"/>
       <c r="E407" s="40"/>
       <c r="F407" s="40"/>
       <c r="G407" s="52"/>
-      <c r="H407" s="40"/>
+      <c r="H407" s="50"/>
       <c r="I407" s="36"/>
       <c r="L407" s="46"/>
     </row>
@@ -11214,12 +11317,12 @@
     </row>
     <row r="412" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B412" s="39"/>
-      <c r="C412" s="35"/>
-      <c r="D412" s="35"/>
-      <c r="E412" s="35"/>
-      <c r="F412" s="35"/>
+      <c r="C412" s="40"/>
+      <c r="D412" s="40"/>
+      <c r="E412" s="40"/>
+      <c r="F412" s="40"/>
       <c r="G412" s="52"/>
-      <c r="H412" s="35"/>
+      <c r="H412" s="40"/>
       <c r="I412" s="36"/>
       <c r="L412" s="46"/>
     </row>
@@ -11236,12 +11339,12 @@
     </row>
     <row r="414" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B414" s="39"/>
-      <c r="C414" s="40"/>
-      <c r="D414" s="40"/>
-      <c r="E414" s="40"/>
-      <c r="F414" s="40"/>
+      <c r="C414" s="35"/>
+      <c r="D414" s="35"/>
+      <c r="E414" s="35"/>
+      <c r="F414" s="35"/>
       <c r="G414" s="52"/>
-      <c r="H414" s="40"/>
+      <c r="H414" s="35"/>
       <c r="I414" s="36"/>
       <c r="L414" s="46"/>
     </row>
@@ -11252,16 +11355,16 @@
       <c r="E415" s="40"/>
       <c r="F415" s="40"/>
       <c r="G415" s="52"/>
-      <c r="H415" s="35"/>
+      <c r="H415" s="40"/>
       <c r="I415" s="36"/>
       <c r="L415" s="46"/>
     </row>
     <row r="416" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B416" s="39"/>
-      <c r="C416" s="35"/>
-      <c r="D416" s="35"/>
-      <c r="E416" s="35"/>
-      <c r="F416" s="35"/>
+      <c r="C416" s="40"/>
+      <c r="D416" s="40"/>
+      <c r="E416" s="40"/>
+      <c r="F416" s="40"/>
       <c r="G416" s="52"/>
       <c r="H416" s="35"/>
       <c r="I416" s="36"/>
@@ -11269,12 +11372,12 @@
     </row>
     <row r="417" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B417" s="39"/>
-      <c r="C417" s="40"/>
-      <c r="D417" s="40"/>
-      <c r="E417" s="40"/>
-      <c r="F417" s="40"/>
+      <c r="C417" s="35"/>
+      <c r="D417" s="35"/>
+      <c r="E417" s="35"/>
+      <c r="F417" s="35"/>
       <c r="G417" s="52"/>
-      <c r="H417" s="40"/>
+      <c r="H417" s="35"/>
       <c r="I417" s="36"/>
       <c r="L417" s="46"/>
     </row>
@@ -11502,8 +11605,8 @@
       <c r="B438" s="39"/>
       <c r="C438" s="40"/>
       <c r="D438" s="40"/>
-      <c r="E438" s="35"/>
-      <c r="F438" s="35"/>
+      <c r="E438" s="40"/>
+      <c r="F438" s="40"/>
       <c r="G438" s="52"/>
       <c r="H438" s="40"/>
       <c r="I438" s="36"/>
@@ -11513,8 +11616,8 @@
       <c r="B439" s="39"/>
       <c r="C439" s="40"/>
       <c r="D439" s="40"/>
-      <c r="E439" s="40"/>
-      <c r="F439" s="40"/>
+      <c r="E439" s="35"/>
+      <c r="F439" s="35"/>
       <c r="G439" s="52"/>
       <c r="H439" s="40"/>
       <c r="I439" s="36"/>
@@ -11544,7 +11647,7 @@
     </row>
     <row r="442" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B442" s="39"/>
-      <c r="C442" s="48"/>
+      <c r="C442" s="40"/>
       <c r="D442" s="40"/>
       <c r="E442" s="40"/>
       <c r="F442" s="40"/>
@@ -11555,10 +11658,11 @@
     </row>
     <row r="443" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B443" s="39"/>
-      <c r="C443" s="40"/>
+      <c r="C443" s="48"/>
       <c r="D443" s="40"/>
       <c r="E443" s="40"/>
       <c r="F443" s="40"/>
+      <c r="G443" s="52"/>
       <c r="H443" s="40"/>
       <c r="I443" s="36"/>
       <c r="L443" s="46"/>
@@ -11717,8 +11821,8 @@
       <c r="B459" s="39"/>
       <c r="C459" s="40"/>
       <c r="D459" s="40"/>
-      <c r="E459" s="39"/>
-      <c r="F459" s="39"/>
+      <c r="E459" s="40"/>
+      <c r="F459" s="40"/>
       <c r="H459" s="40"/>
       <c r="I459" s="36"/>
       <c r="L459" s="46"/>
@@ -11727,8 +11831,8 @@
       <c r="B460" s="39"/>
       <c r="C460" s="40"/>
       <c r="D460" s="40"/>
-      <c r="E460" s="40"/>
-      <c r="F460" s="40"/>
+      <c r="E460" s="39"/>
+      <c r="F460" s="39"/>
       <c r="H460" s="40"/>
       <c r="I460" s="36"/>
       <c r="L460" s="46"/>
@@ -11783,12 +11887,22 @@
       <c r="I465" s="36"/>
       <c r="L465" s="46"/>
     </row>
+    <row r="466" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B466" s="39"/>
+      <c r="C466" s="40"/>
+      <c r="D466" s="40"/>
+      <c r="E466" s="40"/>
+      <c r="F466" s="40"/>
+      <c r="H466" s="40"/>
+      <c r="I466" s="36"/>
+      <c r="L466" s="46"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B394:B465" xr:uid="{8C405A5E-7043-445E-843A-77F75AAA649B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B395:B466" xr:uid="{8C405A5E-7043-445E-843A-77F75AAA649B}">
       <formula1>"Critical Error,Error,Warning"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B393" xr:uid="{6F406B99-E9E0-45D7-8C45-0DC455333DE4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B394" xr:uid="{6F406B99-E9E0-45D7-8C45-0DC455333DE4}">
       <formula1>"C,E,W"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11798,6 +11912,110 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9205B20B-FF03-4195-BC48-128CA8A89C02}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" customWidth="1"/>
+    <col min="4" max="4" width="54.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C5" t="s">
+        <v>661</v>
+      </c>
+      <c r="D5" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>651</v>
+      </c>
+      <c r="C6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="102" t="s">
+        <v>662</v>
+      </c>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC7A87C-3553-4505-86D7-E35A1A59974A}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11860,8 +12078,8 @@
       <c r="A3" t="s">
         <v>284</v>
       </c>
-      <c r="B3" s="56">
-        <v>45785</v>
+      <c r="B3" s="89">
+        <v>46303</v>
       </c>
       <c r="C3" t="s">
         <v>217</v>
@@ -11869,8 +12087,8 @@
       <c r="D3" s="57">
         <v>2001</v>
       </c>
-      <c r="E3">
-        <v>2025</v>
+      <c r="E3" s="73">
+        <v>2026</v>
       </c>
       <c r="H3" s="58" t="s">
         <v>223</v>
